--- a/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785C3881-5609-40F6-B47C-A1D14CBC1CE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B422E69E-B29B-4A16-A022-F72AB88B8584}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -10604,19 +10604,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>35</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8+E8-G8</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -10644,7 +10648,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>849</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -10679,19 +10683,23 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
-      <c r="D9" s="114"/>
+      <c r="C9" s="113">
+        <v>87</v>
+      </c>
+      <c r="D9" s="114">
+        <v>12</v>
+      </c>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
       <c r="G9" s="78"/>
       <c r="H9" s="79"/>
       <c r="I9" s="80">
         <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K9" s="51"/>
       <c r="L9" s="121"/>
@@ -10719,7 +10727,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -10754,7 +10762,9 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>93</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
@@ -10762,7 +10772,7 @@
       <c r="H10" s="73"/>
       <c r="I10" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -10794,7 +10804,7 @@
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2232</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -10829,7 +10839,9 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>49</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
@@ -10837,7 +10849,7 @@
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
@@ -10869,7 +10881,7 @@
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1176</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -10904,19 +10916,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>9</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -10944,7 +10960,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -10979,47 +10995,63 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3578</v>
+      </c>
+      <c r="D13" s="114">
+        <v>5</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>28</v>
+      </c>
+      <c r="H13" s="79">
+        <v>9</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3550</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K13" s="53"/>
       <c r="L13" s="121"/>
       <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
+      <c r="N13" s="121">
+        <v>11</v>
+      </c>
+      <c r="O13" s="121">
+        <v>4</v>
+      </c>
+      <c r="P13" s="121">
+        <v>17</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>5</v>
+      </c>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>672</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>85196</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -11061,19 +11093,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" ref="J14:J59" si="7">D14-H14</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -11101,7 +11137,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -11136,7 +11172,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>2</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -11144,7 +11182,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="7"/>
@@ -11176,7 +11214,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -11361,7 +11399,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -11369,7 +11409,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="7"/>
@@ -11401,7 +11441,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -11511,19 +11551,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -11551,7 +11595,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -11586,7 +11630,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -11594,7 +11640,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="7"/>
@@ -11626,7 +11672,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -11661,7 +11707,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -11669,7 +11717,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="7"/>
@@ -11701,7 +11749,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -11736,19 +11784,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -11776,7 +11828,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -11818,19 +11870,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -11858,7 +11914,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -11900,7 +11956,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>5</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -11908,7 +11966,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="7"/>
@@ -11940,7 +11998,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -11975,30 +12033,38 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>57</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
-      <c r="G26" s="76"/>
+      <c r="G26" s="76">
+        <v>2</v>
+      </c>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
       <c r="M26" s="112"/>
       <c r="N26" s="112"/>
       <c r="O26" s="112"/>
-      <c r="P26" s="112"/>
+      <c r="P26" s="112">
+        <v>2</v>
+      </c>
       <c r="Q26" s="120"/>
       <c r="R26" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" s="124">
         <f t="shared" si="8"/>
@@ -12007,15 +12073,15 @@
       <c r="T26" s="41"/>
       <c r="U26" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V26" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1321</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -12031,7 +12097,9 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="110"/>
+      <c r="C27" s="110">
+        <v>1</v>
+      </c>
       <c r="D27" s="111"/>
       <c r="E27" s="112"/>
       <c r="F27" s="112"/>
@@ -12039,7 +12107,7 @@
       <c r="H27" s="73"/>
       <c r="I27" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="77">
         <f t="shared" si="7"/>
@@ -12071,7 +12139,7 @@
       </c>
       <c r="W27" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X27" s="27"/>
       <c r="Y27" s="2"/>
@@ -12090,7 +12158,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>4</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -12098,7 +12168,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="7"/>
@@ -12130,7 +12200,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -12149,15 +12219,19 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>20</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
+      <c r="G29" s="76">
+        <v>4</v>
+      </c>
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="7"/>
@@ -12168,11 +12242,13 @@
       <c r="M29" s="112"/>
       <c r="N29" s="112"/>
       <c r="O29" s="112"/>
-      <c r="P29" s="112"/>
+      <c r="P29" s="112">
+        <v>4</v>
+      </c>
       <c r="Q29" s="120"/>
       <c r="R29" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S29" s="124">
         <f t="shared" si="8"/>
@@ -12181,15 +12257,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V29" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W29" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -12208,19 +12284,23 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>29</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
       <c r="G30" s="76"/>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
@@ -12248,7 +12328,7 @@
       </c>
       <c r="W30" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>701</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -12260,7 +12340,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>15</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
@@ -12268,7 +12350,7 @@
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="7"/>
@@ -12300,7 +12382,7 @@
       </c>
       <c r="W31" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -12312,7 +12394,9 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="110"/>
+      <c r="C32" s="110">
+        <v>3</v>
+      </c>
       <c r="D32" s="111"/>
       <c r="E32" s="112"/>
       <c r="F32" s="112"/>
@@ -12320,7 +12404,7 @@
       <c r="H32" s="73"/>
       <c r="I32" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" s="77">
         <f t="shared" si="7"/>
@@ -12352,7 +12436,7 @@
       </c>
       <c r="W32" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X32" s="27"/>
     </row>
@@ -12416,7 +12500,9 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>2</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
@@ -12424,7 +12510,7 @@
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" s="77">
         <f t="shared" si="7"/>
@@ -12456,7 +12542,7 @@
       </c>
       <c r="W34" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -12468,19 +12554,23 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>209</v>
+      </c>
+      <c r="D35" s="111">
+        <v>2</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
       <c r="G35" s="76"/>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="112"/>
@@ -12508,7 +12598,7 @@
       </c>
       <c r="W35" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5018</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -12624,30 +12714,40 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>4291</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>75</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4216</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
       <c r="L38" s="121"/>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>20</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>55</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="8"/>
@@ -12656,15 +12756,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>25297</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -12676,7 +12776,9 @@
       <c r="B39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="110"/>
+      <c r="C39" s="110">
+        <v>1</v>
+      </c>
       <c r="D39" s="111"/>
       <c r="E39" s="112"/>
       <c r="F39" s="112"/>
@@ -12684,7 +12786,7 @@
       <c r="H39" s="73"/>
       <c r="I39" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="77">
         <f t="shared" si="7"/>
@@ -12716,7 +12818,7 @@
       </c>
       <c r="W39" s="129">
         <f t="shared" ref="W39:W41" si="11">I39*24+J39</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X39" s="27"/>
     </row>
@@ -12780,19 +12882,23 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>208</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
       <c r="G41" s="149"/>
       <c r="H41" s="150"/>
       <c r="I41" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="153"/>
       <c r="L41" s="154"/>
@@ -12820,7 +12926,7 @@
       </c>
       <c r="W41" s="159">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>5012</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -12832,15 +12938,19 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>127</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>6</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="181">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="7"/>
@@ -12849,13 +12959,17 @@
       <c r="K42" s="169"/>
       <c r="L42" s="165"/>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>2</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>4</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="8"/>
@@ -12864,15 +12978,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>1452</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -12927,30 +13041,40 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>45228</v>
+      </c>
+      <c r="D44" s="114">
+        <v>1</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>979</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="182">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>44249</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="51"/>
       <c r="L44" s="121"/>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>431</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>548</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>979</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="8"/>
@@ -12959,15 +13083,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>5874</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>979</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>265495</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -13075,7 +13199,9 @@
       <c r="B47" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="110"/>
+      <c r="C47" s="110">
+        <v>1</v>
+      </c>
       <c r="D47" s="111"/>
       <c r="E47" s="112"/>
       <c r="F47" s="112"/>
@@ -13083,7 +13209,7 @@
       <c r="H47" s="73"/>
       <c r="I47" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" s="77">
         <f t="shared" si="7"/>
@@ -13115,7 +13241,7 @@
       </c>
       <c r="W47" s="129">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X47" s="27"/>
     </row>
@@ -13127,19 +13253,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2702</v>
+      </c>
+      <c r="D48" s="142">
+        <v>3</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
       <c r="G48" s="143"/>
       <c r="H48" s="139"/>
       <c r="I48" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2702</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
@@ -13167,7 +13297,7 @@
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16215</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -13179,7 +13309,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -13187,7 +13319,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="7"/>
@@ -13219,7 +13351,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -13231,7 +13363,9 @@
       <c r="B50" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="110"/>
+      <c r="C50" s="110">
+        <v>10</v>
+      </c>
       <c r="D50" s="111"/>
       <c r="E50" s="112"/>
       <c r="F50" s="112"/>
@@ -13239,7 +13373,7 @@
       <c r="H50" s="73"/>
       <c r="I50" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J50" s="77">
         <f t="shared" si="7"/>
@@ -13271,7 +13405,7 @@
       </c>
       <c r="W50" s="129">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X50" s="27"/>
     </row>
@@ -13335,7 +13469,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -13343,7 +13479,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="78">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="7"/>
@@ -13375,7 +13511,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -13440,7 +13576,7 @@
         <v>78</v>
       </c>
       <c r="C54" s="110">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
@@ -13449,7 +13585,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="7"/>
@@ -13481,7 +13617,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="20"/>
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -13696,11 +13832,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>9</v>
+        <v>56862</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -13709,19 +13845,19 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1094</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>9</v>
+        <v>55768</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
@@ -13734,40 +13870,40 @@
       </c>
       <c r="N60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R60" s="85">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1094</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>7212</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
+        <v>1094</v>
       </c>
       <c r="W60" s="180">
         <f>SUM(W8:W59)</f>
-        <v>216</v>
+        <v>415489</v>
       </c>
       <c r="X60" s="45"/>
     </row>
@@ -14509,19 +14645,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>35</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8+E8-G8</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -14549,7 +14689,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>849</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -14584,19 +14724,23 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
-      <c r="D9" s="114"/>
+      <c r="C9" s="113">
+        <v>87</v>
+      </c>
+      <c r="D9" s="114">
+        <v>12</v>
+      </c>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
       <c r="G9" s="78"/>
       <c r="H9" s="79"/>
       <c r="I9" s="80">
         <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K9" s="51"/>
       <c r="L9" s="121"/>
@@ -14624,7 +14768,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -14659,7 +14803,9 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>93</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
@@ -14667,7 +14813,7 @@
       <c r="H10" s="73"/>
       <c r="I10" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -14699,7 +14845,7 @@
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2232</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -14734,15 +14880,19 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>49</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
-      <c r="G11" s="76"/>
+      <c r="G11" s="76">
+        <v>2</v>
+      </c>
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
@@ -14751,13 +14901,15 @@
       <c r="K11" s="41"/>
       <c r="L11" s="112"/>
       <c r="M11" s="112"/>
-      <c r="N11" s="112"/>
+      <c r="N11" s="112">
+        <v>2</v>
+      </c>
       <c r="O11" s="112"/>
       <c r="P11" s="112"/>
       <c r="Q11" s="120"/>
       <c r="R11" s="86">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" s="124">
         <f t="shared" si="1"/>
@@ -14766,15 +14918,15 @@
       <c r="T11" s="41"/>
       <c r="U11" s="107">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V11" s="130">
         <f>U11/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -14809,19 +14961,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>9</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -14849,7 +15005,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -14884,47 +15040,61 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3549</v>
+      </c>
+      <c r="D13" s="114">
+        <v>20</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>18</v>
+      </c>
+      <c r="H13" s="79">
+        <v>10</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3531</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
+      <c r="L13" s="121">
+        <v>8</v>
+      </c>
       <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
+      <c r="N13" s="121">
+        <v>10</v>
+      </c>
+      <c r="O13" s="121">
+        <v>10</v>
+      </c>
       <c r="P13" s="121"/>
       <c r="Q13" s="122"/>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>84754</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -14966,19 +15136,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" ref="J14:J59" si="7">D14-H14</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -15006,7 +15180,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -15041,7 +15215,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>2</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -15049,7 +15225,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="7"/>
@@ -15081,7 +15257,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -15266,7 +15442,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -15274,7 +15452,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="7"/>
@@ -15306,7 +15484,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -15416,19 +15594,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -15456,7 +15638,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -15491,7 +15673,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -15499,7 +15683,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="7"/>
@@ -15531,7 +15715,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -15566,7 +15750,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -15574,7 +15760,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="7"/>
@@ -15606,7 +15792,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -15641,19 +15827,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -15681,7 +15871,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -15723,19 +15913,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -15763,7 +15957,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -15805,7 +15999,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>5</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -15813,7 +16009,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="7"/>
@@ -15845,7 +16041,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -15880,19 +16076,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>55</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
       <c r="G26" s="76"/>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
@@ -15920,7 +16120,7 @@
       </c>
       <c r="W26" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1321</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -15936,11 +16136,15 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="110"/>
+      <c r="C27" s="110">
+        <v>1</v>
+      </c>
       <c r="D27" s="111"/>
       <c r="E27" s="112"/>
       <c r="F27" s="112"/>
-      <c r="G27" s="76"/>
+      <c r="G27" s="76">
+        <v>1</v>
+      </c>
       <c r="H27" s="73"/>
       <c r="I27" s="73">
         <f t="shared" si="4"/>
@@ -15953,13 +16157,15 @@
       <c r="K27" s="42"/>
       <c r="L27" s="112"/>
       <c r="M27" s="112"/>
-      <c r="N27" s="112"/>
+      <c r="N27" s="112">
+        <v>1</v>
+      </c>
       <c r="O27" s="112"/>
       <c r="P27" s="112"/>
       <c r="Q27" s="120"/>
       <c r="R27" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" s="124">
         <f t="shared" si="8"/>
@@ -15968,11 +16174,11 @@
       <c r="T27" s="42"/>
       <c r="U27" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V27" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="129">
         <f t="shared" si="9"/>
@@ -15995,7 +16201,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>4</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -16003,7 +16211,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="7"/>
@@ -16035,7 +16243,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -16054,15 +16262,19 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>16</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
+      <c r="G29" s="76">
+        <v>1</v>
+      </c>
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="7"/>
@@ -16071,13 +16283,15 @@
       <c r="K29" s="42"/>
       <c r="L29" s="112"/>
       <c r="M29" s="112"/>
-      <c r="N29" s="112"/>
+      <c r="N29" s="112">
+        <v>1</v>
+      </c>
       <c r="O29" s="112"/>
       <c r="P29" s="112"/>
       <c r="Q29" s="120"/>
       <c r="R29" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" s="124">
         <f t="shared" si="8"/>
@@ -16086,15 +16300,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V29" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -16113,19 +16327,23 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>29</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
       <c r="G30" s="76"/>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
@@ -16153,7 +16371,7 @@
       </c>
       <c r="W30" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>701</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -16165,7 +16383,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>15</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
@@ -16173,7 +16393,7 @@
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="7"/>
@@ -16205,7 +16425,7 @@
       </c>
       <c r="W31" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -16217,15 +16437,19 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="110"/>
+      <c r="C32" s="110">
+        <v>3</v>
+      </c>
       <c r="D32" s="111"/>
       <c r="E32" s="112"/>
       <c r="F32" s="112"/>
-      <c r="G32" s="76"/>
+      <c r="G32" s="76">
+        <v>1</v>
+      </c>
       <c r="H32" s="73"/>
       <c r="I32" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" s="77">
         <f t="shared" si="7"/>
@@ -16234,13 +16458,15 @@
       <c r="K32" s="41"/>
       <c r="L32" s="112"/>
       <c r="M32" s="112"/>
-      <c r="N32" s="112"/>
+      <c r="N32" s="112">
+        <v>1</v>
+      </c>
       <c r="O32" s="112"/>
       <c r="P32" s="112"/>
       <c r="Q32" s="120"/>
       <c r="R32" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="124">
         <f t="shared" si="8"/>
@@ -16249,15 +16475,15 @@
       <c r="T32" s="41"/>
       <c r="U32" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V32" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X32" s="27"/>
     </row>
@@ -16321,7 +16547,9 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>2</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
@@ -16329,7 +16557,7 @@
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" s="77">
         <f t="shared" si="7"/>
@@ -16361,7 +16589,7 @@
       </c>
       <c r="W34" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -16373,19 +16601,23 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>209</v>
+      </c>
+      <c r="D35" s="111">
+        <v>2</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
       <c r="G35" s="76"/>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="112"/>
@@ -16413,7 +16645,7 @@
       </c>
       <c r="W35" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5018</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -16529,30 +16761,40 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>4216</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>134</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4082</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
+      <c r="L38" s="121">
+        <v>113</v>
+      </c>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>21</v>
+      </c>
       <c r="O38" s="121"/>
       <c r="P38" s="121"/>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="8"/>
@@ -16561,15 +16803,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>804</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>24493</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -16581,11 +16823,15 @@
       <c r="B39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="110"/>
+      <c r="C39" s="110">
+        <v>1</v>
+      </c>
       <c r="D39" s="111"/>
       <c r="E39" s="112"/>
       <c r="F39" s="112"/>
-      <c r="G39" s="76"/>
+      <c r="G39" s="76">
+        <v>1</v>
+      </c>
       <c r="H39" s="73"/>
       <c r="I39" s="93">
         <f t="shared" si="4"/>
@@ -16598,13 +16844,15 @@
       <c r="K39" s="41"/>
       <c r="L39" s="112"/>
       <c r="M39" s="112"/>
-      <c r="N39" s="112"/>
+      <c r="N39" s="112">
+        <v>1</v>
+      </c>
       <c r="O39" s="112"/>
       <c r="P39" s="112"/>
       <c r="Q39" s="120"/>
       <c r="R39" s="96">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" s="126">
         <f t="shared" si="8"/>
@@ -16613,11 +16861,11 @@
       <c r="T39" s="41"/>
       <c r="U39" s="107">
         <f t="shared" ref="U39:U41" si="10">L39*24+N39*24+P39*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V39" s="109">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W39" s="129">
         <f t="shared" ref="W39:W41" si="11">I39*24+J39</f>
@@ -16685,19 +16933,23 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>208</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
       <c r="G41" s="149"/>
       <c r="H41" s="150"/>
       <c r="I41" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="153"/>
       <c r="L41" s="154"/>
@@ -16725,7 +16977,7 @@
       </c>
       <c r="W41" s="159">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>5012</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -16737,22 +16989,28 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>121</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>15</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="181">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K42" s="169"/>
-      <c r="L42" s="165"/>
+      <c r="L42" s="165">
+        <v>15</v>
+      </c>
       <c r="M42" s="165"/>
       <c r="N42" s="165"/>
       <c r="O42" s="165"/>
@@ -16760,7 +17018,7 @@
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="8"/>
@@ -16769,15 +17027,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -16832,30 +17090,40 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>44249</v>
+      </c>
+      <c r="D44" s="114">
+        <v>1</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>558</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="182">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>43691</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>236</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>322</v>
+      </c>
       <c r="O44" s="121"/>
       <c r="P44" s="121"/>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="8"/>
@@ -16864,15 +17132,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>3348</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>262147</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -16980,11 +17248,15 @@
       <c r="B47" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="110"/>
+      <c r="C47" s="110">
+        <v>1</v>
+      </c>
       <c r="D47" s="111"/>
       <c r="E47" s="112"/>
       <c r="F47" s="112"/>
-      <c r="G47" s="76"/>
+      <c r="G47" s="76">
+        <v>1</v>
+      </c>
       <c r="H47" s="73"/>
       <c r="I47" s="73">
         <f t="shared" si="4"/>
@@ -16997,13 +17269,15 @@
       <c r="K47" s="41"/>
       <c r="L47" s="112"/>
       <c r="M47" s="112"/>
-      <c r="N47" s="112"/>
+      <c r="N47" s="112">
+        <v>1</v>
+      </c>
       <c r="O47" s="112"/>
       <c r="P47" s="112"/>
       <c r="Q47" s="120"/>
       <c r="R47" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" s="124">
         <f t="shared" si="8"/>
@@ -17012,11 +17286,11 @@
       <c r="T47" s="41"/>
       <c r="U47" s="107">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V47" s="130">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" s="129">
         <f t="shared" si="14"/>
@@ -17032,19 +17306,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2702</v>
+      </c>
+      <c r="D48" s="142">
+        <v>3</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
       <c r="G48" s="143"/>
       <c r="H48" s="139"/>
       <c r="I48" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2702</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
@@ -17072,7 +17350,7 @@
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16215</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -17084,7 +17362,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -17092,7 +17372,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="7"/>
@@ -17124,7 +17404,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -17136,7 +17416,9 @@
       <c r="B50" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="110"/>
+      <c r="C50" s="110">
+        <v>10</v>
+      </c>
       <c r="D50" s="111"/>
       <c r="E50" s="112"/>
       <c r="F50" s="112"/>
@@ -17144,7 +17426,7 @@
       <c r="H50" s="73"/>
       <c r="I50" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J50" s="77">
         <f t="shared" si="7"/>
@@ -17176,7 +17458,7 @@
       </c>
       <c r="W50" s="129">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X50" s="27"/>
     </row>
@@ -17240,7 +17522,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -17248,7 +17532,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="78">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="7"/>
@@ -17280,7 +17564,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -17345,7 +17629,7 @@
         <v>78</v>
       </c>
       <c r="C54" s="110">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
@@ -17354,7 +17638,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="7"/>
@@ -17386,7 +17670,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="20"/>
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -17601,11 +17885,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>9</v>
+        <v>55767</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -17614,24 +17898,24 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>732</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>9</v>
+        <v>55035</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="21"/>
@@ -17639,11 +17923,11 @@
       </c>
       <c r="N60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="21"/>
@@ -17655,24 +17939,24 @@
       </c>
       <c r="R60" s="85">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>732</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>4932</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
+        <v>732</v>
       </c>
       <c r="W60" s="180">
         <f>SUM(W8:W59)</f>
-        <v>216</v>
+        <v>410547</v>
       </c>
       <c r="X60" s="45"/>
     </row>

--- a/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B422E69E-B29B-4A16-A022-F72AB88B8584}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B52088-8CD6-48A9-A816-0661AC2F1F58}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -18698,30 +18698,38 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>35</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
-      <c r="G8" s="76"/>
+      <c r="G8" s="76">
+        <v>1</v>
+      </c>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8+E8-G8</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
       <c r="M8" s="112"/>
       <c r="N8" s="112"/>
       <c r="O8" s="112"/>
-      <c r="P8" s="112"/>
+      <c r="P8" s="112">
+        <v>1</v>
+      </c>
       <c r="Q8" s="120"/>
       <c r="R8" s="86">
         <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="124">
         <f t="shared" si="1"/>
@@ -18730,15 +18738,15 @@
       <c r="T8" s="41"/>
       <c r="U8" s="107">
         <f>L8*24+N8*24+P8*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V8" s="130">
         <f>U8/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -18773,19 +18781,23 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
-      <c r="D9" s="114"/>
+      <c r="C9" s="113">
+        <v>87</v>
+      </c>
+      <c r="D9" s="114">
+        <v>12</v>
+      </c>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
       <c r="G9" s="78"/>
       <c r="H9" s="79"/>
       <c r="I9" s="80">
         <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K9" s="51"/>
       <c r="L9" s="121"/>
@@ -18813,7 +18825,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -18848,7 +18860,9 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>93</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
@@ -18856,7 +18870,7 @@
       <c r="H10" s="73"/>
       <c r="I10" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -18888,7 +18902,7 @@
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2232</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -18923,7 +18937,9 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>47</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
@@ -18931,7 +18947,7 @@
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
@@ -18963,7 +18979,7 @@
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -18998,19 +19014,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>9</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -19038,7 +19058,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -19073,47 +19093,63 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3531</v>
+      </c>
+      <c r="D13" s="114">
+        <v>10</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>22</v>
+      </c>
+      <c r="H13" s="79">
+        <v>17</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3509</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="K13" s="53"/>
       <c r="L13" s="121"/>
       <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
+      <c r="N13" s="121">
+        <v>11</v>
+      </c>
+      <c r="O13" s="121">
+        <v>12</v>
+      </c>
+      <c r="P13" s="121">
+        <v>11</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>5</v>
+      </c>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>528</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>84209</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -19155,19 +19191,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" ref="J14:J59" si="7">D14-H14</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -19195,7 +19235,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -19230,7 +19270,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>2</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -19238,7 +19280,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="7"/>
@@ -19270,7 +19312,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -19455,7 +19497,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -19463,7 +19507,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="7"/>
@@ -19495,7 +19539,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -19605,19 +19649,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -19645,7 +19693,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -19680,7 +19728,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -19688,7 +19738,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="7"/>
@@ -19720,7 +19770,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -19755,7 +19805,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -19763,7 +19815,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="7"/>
@@ -19795,7 +19847,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -19830,19 +19882,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -19870,7 +19926,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -19912,19 +19968,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -19952,7 +20012,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -19994,7 +20054,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>5</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -20002,7 +20064,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="7"/>
@@ -20034,7 +20096,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -20069,19 +20131,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>55</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
       <c r="G26" s="76"/>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
@@ -20109,7 +20175,7 @@
       </c>
       <c r="W26" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1321</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -20184,7 +20250,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>4</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -20192,7 +20260,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="7"/>
@@ -20224,7 +20292,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -20243,15 +20311,19 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>15</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
+      <c r="G29" s="76">
+        <v>1</v>
+      </c>
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="7"/>
@@ -20262,11 +20334,13 @@
       <c r="M29" s="112"/>
       <c r="N29" s="112"/>
       <c r="O29" s="112"/>
-      <c r="P29" s="112"/>
+      <c r="P29" s="112">
+        <v>1</v>
+      </c>
       <c r="Q29" s="120"/>
       <c r="R29" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" s="124">
         <f t="shared" si="8"/>
@@ -20275,15 +20349,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V29" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -20302,19 +20376,23 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>29</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
       <c r="G30" s="76"/>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
@@ -20342,7 +20420,7 @@
       </c>
       <c r="W30" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>701</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -20354,7 +20432,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>15</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
@@ -20362,7 +20442,7 @@
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="7"/>
@@ -20394,7 +20474,7 @@
       </c>
       <c r="W31" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -20406,7 +20486,9 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="110"/>
+      <c r="C32" s="110">
+        <v>2</v>
+      </c>
       <c r="D32" s="111"/>
       <c r="E32" s="112"/>
       <c r="F32" s="112"/>
@@ -20414,7 +20496,7 @@
       <c r="H32" s="73"/>
       <c r="I32" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" s="77">
         <f t="shared" si="7"/>
@@ -20446,7 +20528,7 @@
       </c>
       <c r="W32" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X32" s="27"/>
     </row>
@@ -20510,7 +20592,9 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>2</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
@@ -20518,7 +20602,7 @@
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" s="77">
         <f t="shared" si="7"/>
@@ -20550,7 +20634,7 @@
       </c>
       <c r="W34" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -20562,30 +20646,40 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>209</v>
+      </c>
+      <c r="D35" s="111">
+        <v>2</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
-      <c r="G35" s="76"/>
+      <c r="G35" s="76">
+        <v>6</v>
+      </c>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="112"/>
       <c r="M35" s="112"/>
-      <c r="N35" s="112"/>
+      <c r="N35" s="112">
+        <v>3</v>
+      </c>
       <c r="O35" s="112"/>
-      <c r="P35" s="112"/>
+      <c r="P35" s="112">
+        <v>3</v>
+      </c>
       <c r="Q35" s="120"/>
       <c r="R35" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S35" s="124">
         <f t="shared" si="8"/>
@@ -20594,15 +20688,15 @@
       <c r="T35" s="41"/>
       <c r="U35" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V35" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W35" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>4874</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -20718,30 +20812,38 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>4082</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>28</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4054</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
       <c r="L38" s="121"/>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>28</v>
+      </c>
       <c r="O38" s="121"/>
       <c r="P38" s="121"/>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="8"/>
@@ -20750,15 +20852,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>24325</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -20874,30 +20976,40 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>208</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
-      <c r="G41" s="149"/>
+      <c r="G41" s="149">
+        <v>87</v>
+      </c>
       <c r="H41" s="150"/>
       <c r="I41" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="153"/>
       <c r="L41" s="154"/>
       <c r="M41" s="154"/>
-      <c r="N41" s="154"/>
+      <c r="N41" s="154">
+        <v>67</v>
+      </c>
       <c r="O41" s="154"/>
-      <c r="P41" s="154"/>
+      <c r="P41" s="154">
+        <v>20</v>
+      </c>
       <c r="Q41" s="155"/>
       <c r="R41" s="156">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="S41" s="157">
         <f t="shared" si="8"/>
@@ -20906,15 +21018,15 @@
       <c r="T41" s="153"/>
       <c r="U41" s="158">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2088</v>
       </c>
       <c r="V41" s="159">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="W41" s="159">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2924</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -20926,15 +21038,19 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>106</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>24</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="181">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="7"/>
@@ -20943,13 +21059,17 @@
       <c r="K42" s="169"/>
       <c r="L42" s="165"/>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>12</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>12</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="8"/>
@@ -20958,15 +21078,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>984</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -21021,30 +21141,40 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>43691</v>
+      </c>
+      <c r="D44" s="114">
+        <v>1</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>752</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="182">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>42939</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="51"/>
       <c r="L44" s="121"/>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>385</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>367</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>752</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="8"/>
@@ -21053,15 +21183,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>4512</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>752</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>257635</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -21221,19 +21351,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2702</v>
+      </c>
+      <c r="D48" s="142">
+        <v>3</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
       <c r="G48" s="143"/>
       <c r="H48" s="139"/>
       <c r="I48" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2702</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
@@ -21261,7 +21395,7 @@
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16215</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -21273,7 +21407,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -21281,7 +21417,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="7"/>
@@ -21313,7 +21449,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -21325,7 +21461,9 @@
       <c r="B50" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="110"/>
+      <c r="C50" s="110">
+        <v>10</v>
+      </c>
       <c r="D50" s="111"/>
       <c r="E50" s="112"/>
       <c r="F50" s="112"/>
@@ -21333,7 +21471,7 @@
       <c r="H50" s="73"/>
       <c r="I50" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J50" s="77">
         <f t="shared" si="7"/>
@@ -21365,7 +21503,7 @@
       </c>
       <c r="W50" s="129">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X50" s="27"/>
     </row>
@@ -21429,7 +21567,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -21437,7 +21577,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="78">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="7"/>
@@ -21469,7 +21609,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -21534,7 +21674,7 @@
         <v>78</v>
       </c>
       <c r="C54" s="110">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
@@ -21543,7 +21683,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="7"/>
@@ -21575,7 +21715,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="20"/>
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -21790,11 +21930,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>9</v>
+        <v>55035</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -21803,19 +21943,19 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>9</v>
+        <v>54114</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
@@ -21828,40 +21968,40 @@
       </c>
       <c r="N60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R60" s="85">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>7776</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="W60" s="180">
         <f>SUM(W8:W59)</f>
-        <v>216</v>
+        <v>402754</v>
       </c>
       <c r="X60" s="45"/>
     </row>
@@ -22603,19 +22743,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>34</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8+E8-G8</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -22643,7 +22787,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -22678,19 +22822,23 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
-      <c r="D9" s="114"/>
+      <c r="C9" s="113">
+        <v>87</v>
+      </c>
+      <c r="D9" s="114">
+        <v>12</v>
+      </c>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
       <c r="G9" s="78"/>
       <c r="H9" s="79"/>
       <c r="I9" s="80">
         <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K9" s="51"/>
       <c r="L9" s="121"/>
@@ -22718,7 +22866,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -22753,15 +22901,19 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>93</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
-      <c r="G10" s="76"/>
+      <c r="G10" s="76">
+        <v>1</v>
+      </c>
       <c r="H10" s="73"/>
       <c r="I10" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -22772,11 +22924,13 @@
       <c r="M10" s="112"/>
       <c r="N10" s="112"/>
       <c r="O10" s="112"/>
-      <c r="P10" s="112"/>
+      <c r="P10" s="112">
+        <v>1</v>
+      </c>
       <c r="Q10" s="120"/>
       <c r="R10" s="99">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="126">
         <f t="shared" si="1"/>
@@ -22785,15 +22939,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="107">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V10" s="134">
         <f>U10/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2208</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -22828,15 +22982,19 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>47</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
-      <c r="G11" s="76"/>
+      <c r="G11" s="76">
+        <v>1</v>
+      </c>
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
@@ -22847,11 +23005,13 @@
       <c r="M11" s="112"/>
       <c r="N11" s="112"/>
       <c r="O11" s="112"/>
-      <c r="P11" s="112"/>
+      <c r="P11" s="112">
+        <v>1</v>
+      </c>
       <c r="Q11" s="120"/>
       <c r="R11" s="86">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="124">
         <f t="shared" si="1"/>
@@ -22860,15 +23020,15 @@
       <c r="T11" s="41"/>
       <c r="U11" s="107">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="130">
         <f>U11/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1104</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -22903,19 +23063,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>9</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -22943,7 +23107,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -22978,47 +23142,67 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3508</v>
+      </c>
+      <c r="D13" s="114">
+        <v>17</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>27</v>
+      </c>
+      <c r="H13" s="79">
+        <v>26</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3481</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
+      <c r="L13" s="121">
+        <v>3</v>
+      </c>
+      <c r="M13" s="121">
+        <v>17</v>
+      </c>
+      <c r="N13" s="121">
+        <v>10</v>
+      </c>
+      <c r="O13" s="121">
+        <v>5</v>
+      </c>
+      <c r="P13" s="121">
+        <v>14</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>4</v>
+      </c>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>83535</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -23060,19 +23244,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" ref="J14:J59" si="7">D14-H14</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -23100,7 +23288,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -23135,7 +23323,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>2</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -23143,7 +23333,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="7"/>
@@ -23175,7 +23365,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -23360,7 +23550,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -23368,7 +23560,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="7"/>
@@ -23400,7 +23592,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -23510,19 +23702,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -23550,7 +23746,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -23585,7 +23781,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -23593,7 +23791,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="7"/>
@@ -23625,7 +23823,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -23660,7 +23858,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -23668,7 +23868,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="7"/>
@@ -23700,7 +23900,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -23735,19 +23935,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -23775,7 +23979,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -23817,19 +24021,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -23857,7 +24065,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -23899,7 +24107,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>5</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -23907,7 +24117,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="7"/>
@@ -23939,7 +24149,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -23974,19 +24184,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>55</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
       <c r="G26" s="76"/>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
@@ -24014,7 +24228,7 @@
       </c>
       <c r="W26" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1321</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -24089,7 +24303,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>4</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -24097,7 +24313,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="7"/>
@@ -24129,7 +24345,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -24148,7 +24364,9 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>14</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
@@ -24156,7 +24374,7 @@
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="7"/>
@@ -24188,7 +24406,7 @@
       </c>
       <c r="W29" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -24207,19 +24425,23 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>29</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
       <c r="G30" s="76"/>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
@@ -24247,7 +24469,7 @@
       </c>
       <c r="W30" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>701</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -24259,7 +24481,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>15</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
@@ -24267,7 +24491,7 @@
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="7"/>
@@ -24299,7 +24523,7 @@
       </c>
       <c r="W31" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -24311,7 +24535,9 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="110"/>
+      <c r="C32" s="110">
+        <v>2</v>
+      </c>
       <c r="D32" s="111"/>
       <c r="E32" s="112"/>
       <c r="F32" s="112"/>
@@ -24319,7 +24545,7 @@
       <c r="H32" s="73"/>
       <c r="I32" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" s="77">
         <f t="shared" si="7"/>
@@ -24351,7 +24577,7 @@
       </c>
       <c r="W32" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X32" s="27"/>
     </row>
@@ -24415,7 +24641,9 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>2</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
@@ -24423,7 +24651,7 @@
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" s="77">
         <f t="shared" si="7"/>
@@ -24455,7 +24683,7 @@
       </c>
       <c r="W34" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -24467,30 +24695,40 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>203</v>
+      </c>
+      <c r="D35" s="111">
+        <v>2</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
-      <c r="G35" s="76"/>
+      <c r="G35" s="76">
+        <v>3</v>
+      </c>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" s="41"/>
-      <c r="L35" s="112"/>
+      <c r="L35" s="112">
+        <v>2</v>
+      </c>
       <c r="M35" s="112"/>
-      <c r="N35" s="112"/>
+      <c r="N35" s="112">
+        <v>1</v>
+      </c>
       <c r="O35" s="112"/>
       <c r="P35" s="112"/>
       <c r="Q35" s="120"/>
       <c r="R35" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S35" s="124">
         <f t="shared" si="8"/>
@@ -24499,15 +24737,15 @@
       <c r="T35" s="41"/>
       <c r="U35" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V35" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W35" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>4802</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -24623,30 +24861,42 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>4054</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>169</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3885</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
+      <c r="L38" s="121">
+        <v>37</v>
+      </c>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>24</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>108</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="8"/>
@@ -24655,15 +24905,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>1014</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>23311</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -24779,30 +25029,38 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>121</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
-      <c r="G41" s="149"/>
+      <c r="G41" s="149">
+        <v>1</v>
+      </c>
       <c r="H41" s="150"/>
       <c r="I41" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="153"/>
       <c r="L41" s="154"/>
       <c r="M41" s="154"/>
       <c r="N41" s="154"/>
       <c r="O41" s="154"/>
-      <c r="P41" s="154"/>
+      <c r="P41" s="154">
+        <v>1</v>
+      </c>
       <c r="Q41" s="155"/>
       <c r="R41" s="156">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" s="157">
         <f t="shared" si="8"/>
@@ -24811,15 +25069,15 @@
       <c r="T41" s="153"/>
       <c r="U41" s="158">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V41" s="159">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="159">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -24831,30 +25089,40 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>82</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>31</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="181">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K42" s="169"/>
-      <c r="L42" s="165"/>
+      <c r="L42" s="165">
+        <v>15</v>
+      </c>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>12</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>4</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="8"/>
@@ -24863,15 +25131,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -24926,30 +25194,42 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>42939</v>
+      </c>
+      <c r="D44" s="114">
+        <v>1</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>1242</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="182">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>41697</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>482</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>373</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>387</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1242</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="8"/>
@@ -24958,15 +25238,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>7452</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>1242</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>250183</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -25126,19 +25406,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2702</v>
+      </c>
+      <c r="D48" s="142">
+        <v>3</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
       <c r="G48" s="143"/>
       <c r="H48" s="139"/>
       <c r="I48" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2702</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
@@ -25166,7 +25450,7 @@
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16215</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -25178,7 +25462,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -25186,7 +25472,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="7"/>
@@ -25218,7 +25504,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -25230,7 +25516,9 @@
       <c r="B50" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="110"/>
+      <c r="C50" s="110">
+        <v>10</v>
+      </c>
       <c r="D50" s="111"/>
       <c r="E50" s="112"/>
       <c r="F50" s="112"/>
@@ -25238,7 +25526,7 @@
       <c r="H50" s="73"/>
       <c r="I50" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J50" s="77">
         <f t="shared" si="7"/>
@@ -25270,7 +25558,7 @@
       </c>
       <c r="W50" s="129">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X50" s="27"/>
     </row>
@@ -25334,7 +25622,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -25342,7 +25632,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="78">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="7"/>
@@ -25374,7 +25664,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -25439,7 +25729,7 @@
         <v>78</v>
       </c>
       <c r="C54" s="110">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
@@ -25448,7 +25738,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="7"/>
@@ -25480,7 +25770,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="20"/>
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -25695,11 +25985,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>9</v>
+        <v>54113</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -25708,65 +25998,65 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1475</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>9</v>
+        <v>52638</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>539</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R60" s="85">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1475</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>9630</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
+        <v>1475</v>
       </c>
       <c r="W60" s="180">
         <f>SUM(W8:W59)</f>
-        <v>216</v>
+        <v>393098</v>
       </c>
       <c r="X60" s="45"/>
     </row>

--- a/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B52088-8CD6-48A9-A816-0661AC2F1F58}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E71085B-C95D-4F36-8499-F2B7F0B6BD47}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -26798,19 +26798,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>34</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8+E8-G8</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -26838,7 +26842,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -26873,19 +26877,23 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
-      <c r="D9" s="114"/>
+      <c r="C9" s="113">
+        <v>87</v>
+      </c>
+      <c r="D9" s="114">
+        <v>12</v>
+      </c>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
       <c r="G9" s="78"/>
       <c r="H9" s="79"/>
       <c r="I9" s="80">
         <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K9" s="51"/>
       <c r="L9" s="121"/>
@@ -26913,7 +26921,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -26948,7 +26956,9 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>92</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
@@ -26956,7 +26966,7 @@
       <c r="H10" s="73"/>
       <c r="I10" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -26988,7 +26998,7 @@
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2208</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -27023,7 +27033,9 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>46</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
@@ -27031,7 +27043,7 @@
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
@@ -27063,7 +27075,7 @@
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1104</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -27098,19 +27110,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>9</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -27138,7 +27154,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -27173,47 +27189,61 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3480</v>
+      </c>
+      <c r="D13" s="114">
+        <v>15</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>18</v>
+      </c>
+      <c r="H13" s="79">
+        <v>1</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3462</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K13" s="53"/>
       <c r="L13" s="121"/>
       <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
+      <c r="N13" s="121">
+        <v>11</v>
+      </c>
       <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
+      <c r="P13" s="121">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>1</v>
+      </c>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>83102</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -27255,19 +27285,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" ref="J14:J59" si="7">D14-H14</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -27295,7 +27329,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -27330,7 +27364,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>2</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -27338,7 +27374,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="7"/>
@@ -27370,7 +27406,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -27555,7 +27591,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -27563,7 +27601,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="7"/>
@@ -27595,7 +27633,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -27705,19 +27743,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -27745,7 +27787,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -27780,7 +27822,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -27788,7 +27832,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="7"/>
@@ -27820,7 +27864,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -27855,7 +27899,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -27863,7 +27909,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="7"/>
@@ -27895,7 +27941,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -27930,19 +27976,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -27970,7 +28020,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -28012,19 +28062,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -28052,7 +28106,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -28094,7 +28148,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>5</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -28102,7 +28158,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="7"/>
@@ -28134,7 +28190,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -28169,19 +28225,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>55</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
       <c r="G26" s="76"/>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
@@ -28209,7 +28269,7 @@
       </c>
       <c r="W26" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1321</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -28284,7 +28344,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>4</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -28292,7 +28354,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="7"/>
@@ -28324,7 +28386,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -28343,15 +28405,19 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>14</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
+      <c r="G29" s="76">
+        <v>2</v>
+      </c>
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="7"/>
@@ -28362,11 +28428,13 @@
       <c r="M29" s="112"/>
       <c r="N29" s="112"/>
       <c r="O29" s="112"/>
-      <c r="P29" s="112"/>
+      <c r="P29" s="112">
+        <v>2</v>
+      </c>
       <c r="Q29" s="120"/>
       <c r="R29" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S29" s="124">
         <f t="shared" si="8"/>
@@ -28375,15 +28443,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V29" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W29" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -28402,19 +28470,23 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>29</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
       <c r="G30" s="76"/>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
@@ -28442,7 +28514,7 @@
       </c>
       <c r="W30" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>701</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -28454,7 +28526,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>15</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
@@ -28462,7 +28536,7 @@
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="7"/>
@@ -28494,7 +28568,7 @@
       </c>
       <c r="W31" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -28506,7 +28580,9 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="110"/>
+      <c r="C32" s="110">
+        <v>2</v>
+      </c>
       <c r="D32" s="111"/>
       <c r="E32" s="112"/>
       <c r="F32" s="112"/>
@@ -28514,7 +28590,7 @@
       <c r="H32" s="73"/>
       <c r="I32" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" s="77">
         <f t="shared" si="7"/>
@@ -28546,7 +28622,7 @@
       </c>
       <c r="W32" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X32" s="27"/>
     </row>
@@ -28610,7 +28686,9 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>2</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
@@ -28618,7 +28696,7 @@
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" s="77">
         <f t="shared" si="7"/>
@@ -28650,7 +28728,7 @@
       </c>
       <c r="W34" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -28662,30 +28740,38 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>200</v>
+      </c>
+      <c r="D35" s="111">
+        <v>2</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
-      <c r="G35" s="76"/>
+      <c r="G35" s="76">
+        <v>2</v>
+      </c>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="112"/>
       <c r="M35" s="112"/>
       <c r="N35" s="112"/>
       <c r="O35" s="112"/>
-      <c r="P35" s="112"/>
+      <c r="P35" s="112">
+        <v>2</v>
+      </c>
       <c r="Q35" s="120"/>
       <c r="R35" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S35" s="124">
         <f t="shared" si="8"/>
@@ -28694,15 +28780,15 @@
       <c r="T35" s="41"/>
       <c r="U35" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V35" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W35" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>4754</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -28818,30 +28904,40 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>3885</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>120</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3765</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
       <c r="L38" s="121"/>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>12</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>108</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="8"/>
@@ -28850,15 +28946,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>22591</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -28974,19 +29070,23 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>120</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
       <c r="G41" s="149"/>
       <c r="H41" s="150"/>
       <c r="I41" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="153"/>
       <c r="L41" s="154"/>
@@ -29014,7 +29114,7 @@
       </c>
       <c r="W41" s="159">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -29026,15 +29126,19 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>51</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>15</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="181">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="7"/>
@@ -29043,13 +29147,17 @@
       <c r="K42" s="169"/>
       <c r="L42" s="165"/>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>9</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>6</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="8"/>
@@ -29058,15 +29166,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -29121,30 +29229,40 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>41696</v>
+      </c>
+      <c r="D44" s="114">
+        <v>4</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>553</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="182">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>41143</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K44" s="51"/>
       <c r="L44" s="121"/>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>273</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>280</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="8"/>
@@ -29153,15 +29271,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>246862</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -29321,19 +29439,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2702</v>
+      </c>
+      <c r="D48" s="142">
+        <v>3</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
       <c r="G48" s="143"/>
       <c r="H48" s="139"/>
       <c r="I48" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2702</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
@@ -29361,7 +29483,7 @@
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16215</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -29373,7 +29495,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -29381,7 +29505,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="7"/>
@@ -29413,7 +29537,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -29425,7 +29549,9 @@
       <c r="B50" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="110"/>
+      <c r="C50" s="110">
+        <v>10</v>
+      </c>
       <c r="D50" s="111"/>
       <c r="E50" s="112"/>
       <c r="F50" s="112"/>
@@ -29433,7 +29559,7 @@
       <c r="H50" s="73"/>
       <c r="I50" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J50" s="77">
         <f t="shared" si="7"/>
@@ -29465,7 +29591,7 @@
       </c>
       <c r="W50" s="129">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X50" s="27"/>
     </row>
@@ -29529,7 +29655,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -29537,7 +29665,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="78">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="7"/>
@@ -29569,7 +29697,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -29634,7 +29762,7 @@
         <v>78</v>
       </c>
       <c r="C54" s="110">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
@@ -29643,7 +29771,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="7"/>
@@ -29675,7 +29803,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="20"/>
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -29890,11 +30018,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>9</v>
+        <v>52636</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -29903,19 +30031,19 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>710</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>9</v>
+        <v>51926</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
@@ -29928,7 +30056,7 @@
       </c>
       <c r="N60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="21"/>
@@ -29936,32 +30064,32 @@
       </c>
       <c r="P60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" s="85">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>710</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>4746</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
+        <v>710</v>
       </c>
       <c r="W60" s="180">
         <f>SUM(W8:W59)</f>
-        <v>216</v>
+        <v>388348</v>
       </c>
       <c r="X60" s="45"/>
     </row>

--- a/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E71085B-C95D-4F36-8499-F2B7F0B6BD47}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B22092-636C-44CC-AD1C-3E0DDD5C39BD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -30831,19 +30831,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>34</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8+E8-G8</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -30871,7 +30875,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -30906,19 +30910,23 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
-      <c r="D9" s="114"/>
+      <c r="C9" s="113">
+        <v>87</v>
+      </c>
+      <c r="D9" s="114">
+        <v>12</v>
+      </c>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
       <c r="G9" s="78"/>
       <c r="H9" s="79"/>
       <c r="I9" s="80">
         <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K9" s="51"/>
       <c r="L9" s="121"/>
@@ -30946,7 +30954,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -30981,15 +30989,19 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>92</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
-      <c r="G10" s="76"/>
+      <c r="G10" s="76">
+        <v>1</v>
+      </c>
       <c r="H10" s="73"/>
       <c r="I10" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -30998,13 +31010,15 @@
       <c r="K10" s="41"/>
       <c r="L10" s="112"/>
       <c r="M10" s="112"/>
-      <c r="N10" s="112"/>
+      <c r="N10" s="112">
+        <v>1</v>
+      </c>
       <c r="O10" s="112"/>
       <c r="P10" s="112"/>
       <c r="Q10" s="120"/>
       <c r="R10" s="99">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="126">
         <f t="shared" si="1"/>
@@ -31013,15 +31027,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="107">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V10" s="134">
         <f>U10/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2184</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -31056,7 +31070,9 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>46</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
@@ -31064,7 +31080,7 @@
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
@@ -31096,7 +31112,7 @@
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1104</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -31131,19 +31147,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>9</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -31171,7 +31191,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -31206,47 +31226,67 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3462</v>
+      </c>
+      <c r="D13" s="114">
+        <v>14</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>34</v>
+      </c>
+      <c r="H13" s="79">
+        <v>27</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3428</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
+      <c r="L13" s="121">
+        <v>6</v>
+      </c>
+      <c r="M13" s="121">
+        <v>7</v>
+      </c>
+      <c r="N13" s="121">
+        <v>16</v>
+      </c>
+      <c r="O13" s="121">
+        <v>17</v>
+      </c>
+      <c r="P13" s="121">
+        <v>12</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>3</v>
+      </c>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>82259</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -31288,19 +31328,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" ref="J14:J59" si="7">D14-H14</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -31328,7 +31372,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -31363,7 +31407,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>2</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -31371,7 +31417,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="7"/>
@@ -31403,7 +31449,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -31588,7 +31634,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -31596,7 +31644,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="7"/>
@@ -31628,7 +31676,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -31738,19 +31786,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -31778,7 +31830,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -31813,7 +31865,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -31821,7 +31875,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="7"/>
@@ -31853,7 +31907,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -31888,7 +31942,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -31896,7 +31952,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="7"/>
@@ -31928,7 +31984,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -31963,19 +32019,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -32003,7 +32063,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -32045,19 +32105,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -32085,7 +32149,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -32127,7 +32191,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>5</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -32135,7 +32201,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="7"/>
@@ -32167,7 +32233,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -32202,19 +32268,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>55</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
       <c r="G26" s="76"/>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
@@ -32242,7 +32312,7 @@
       </c>
       <c r="W26" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1321</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -32317,7 +32387,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>4</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -32325,7 +32397,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="7"/>
@@ -32357,7 +32429,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -32376,30 +32448,38 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>12</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
+      <c r="G29" s="76">
+        <v>7</v>
+      </c>
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K29" s="42"/>
-      <c r="L29" s="112"/>
+      <c r="L29" s="112">
+        <v>1</v>
+      </c>
       <c r="M29" s="112"/>
-      <c r="N29" s="112"/>
+      <c r="N29" s="112">
+        <v>6</v>
+      </c>
       <c r="O29" s="112"/>
       <c r="P29" s="112"/>
       <c r="Q29" s="120"/>
       <c r="R29" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S29" s="124">
         <f t="shared" si="8"/>
@@ -32408,15 +32488,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V29" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W29" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -32435,30 +32515,38 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>29</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
-      <c r="G30" s="76"/>
+      <c r="G30" s="76">
+        <v>1</v>
+      </c>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
       <c r="M30" s="112"/>
-      <c r="N30" s="112"/>
+      <c r="N30" s="112">
+        <v>1</v>
+      </c>
       <c r="O30" s="112"/>
       <c r="P30" s="112"/>
       <c r="Q30" s="120"/>
       <c r="R30" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" s="124">
         <f t="shared" si="8"/>
@@ -32467,15 +32555,15 @@
       <c r="T30" s="41"/>
       <c r="U30" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V30" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>677</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -32487,7 +32575,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>15</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
@@ -32495,7 +32585,7 @@
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="7"/>
@@ -32527,7 +32617,7 @@
       </c>
       <c r="W31" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -32539,7 +32629,9 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="110"/>
+      <c r="C32" s="110">
+        <v>2</v>
+      </c>
       <c r="D32" s="111"/>
       <c r="E32" s="112"/>
       <c r="F32" s="112"/>
@@ -32547,7 +32639,7 @@
       <c r="H32" s="73"/>
       <c r="I32" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" s="77">
         <f t="shared" si="7"/>
@@ -32579,7 +32671,7 @@
       </c>
       <c r="W32" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X32" s="27"/>
     </row>
@@ -32643,7 +32735,9 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>2</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
@@ -32651,7 +32745,7 @@
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" s="77">
         <f t="shared" si="7"/>
@@ -32683,7 +32777,7 @@
       </c>
       <c r="W34" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -32695,19 +32789,23 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>198</v>
+      </c>
+      <c r="D35" s="111">
+        <v>2</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
       <c r="G35" s="76"/>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="112"/>
@@ -32735,7 +32833,7 @@
       </c>
       <c r="W35" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>4754</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -32851,30 +32949,42 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>3765</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>225</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3540</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
+      <c r="L38" s="121">
+        <v>8</v>
+      </c>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>125</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>92</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="8"/>
@@ -32883,15 +32993,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>1350</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>21241</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -33007,19 +33117,23 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>120</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
       <c r="G41" s="149"/>
       <c r="H41" s="150"/>
       <c r="I41" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="153"/>
       <c r="L41" s="154"/>
@@ -33047,7 +33161,7 @@
       </c>
       <c r="W41" s="159">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -33059,30 +33173,40 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>36</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>30</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="181">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K42" s="169"/>
-      <c r="L42" s="165"/>
+      <c r="L42" s="165">
+        <v>2</v>
+      </c>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>2</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>26</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="8"/>
@@ -33091,15 +33215,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -33154,30 +33278,42 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>41143</v>
+      </c>
+      <c r="D44" s="114">
+        <v>4</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>1168</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="182">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>39975</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>323</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>361</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>484</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1168</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="8"/>
@@ -33186,15 +33322,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>7008</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>1168</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>239854</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -33354,19 +33490,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2702</v>
+      </c>
+      <c r="D48" s="142">
+        <v>3</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
       <c r="G48" s="143"/>
       <c r="H48" s="139"/>
       <c r="I48" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2702</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
@@ -33394,7 +33534,7 @@
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16215</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -33406,7 +33546,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -33414,7 +33556,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="7"/>
@@ -33446,7 +33588,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -33458,7 +33600,9 @@
       <c r="B50" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="110"/>
+      <c r="C50" s="110">
+        <v>10</v>
+      </c>
       <c r="D50" s="111"/>
       <c r="E50" s="112"/>
       <c r="F50" s="112"/>
@@ -33466,7 +33610,7 @@
       <c r="H50" s="73"/>
       <c r="I50" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J50" s="77">
         <f t="shared" si="7"/>
@@ -33498,7 +33642,7 @@
       </c>
       <c r="W50" s="129">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X50" s="27"/>
     </row>
@@ -33562,7 +33706,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -33570,7 +33716,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="78">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="7"/>
@@ -33602,7 +33748,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -33667,7 +33813,7 @@
         <v>78</v>
       </c>
       <c r="C54" s="110">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
@@ -33676,7 +33822,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="7"/>
@@ -33708,7 +33854,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="20"/>
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -33923,11 +34069,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>9</v>
+        <v>51926</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -33936,65 +34082,65 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1466</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>9</v>
+        <v>50460</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R60" s="85">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1466</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>9750</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
+        <v>1466</v>
       </c>
       <c r="W60" s="180">
         <f>SUM(W8:W59)</f>
-        <v>216</v>
+        <v>378571</v>
       </c>
       <c r="X60" s="45"/>
     </row>

--- a/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB02AE90-C0D4-4895-B38B-1C089245ACC3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A96BD5D-CB2B-45AA-A4E5-8368E9169654}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -6871,30 +6871,38 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>34</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
-      <c r="G8" s="76"/>
+      <c r="G8" s="76">
+        <v>1</v>
+      </c>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8+E8-G8</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
       <c r="M8" s="112"/>
       <c r="N8" s="112"/>
       <c r="O8" s="112"/>
-      <c r="P8" s="112"/>
+      <c r="P8" s="112">
+        <v>1</v>
+      </c>
       <c r="Q8" s="120"/>
       <c r="R8" s="86">
         <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="124">
         <f t="shared" si="1"/>
@@ -6903,15 +6911,15 @@
       <c r="T8" s="41"/>
       <c r="U8" s="107">
         <f>L8*24+N8*24+P8*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V8" s="130">
         <f>U8/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -6946,19 +6954,23 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
-      <c r="D9" s="114"/>
+      <c r="C9" s="113">
+        <v>87</v>
+      </c>
+      <c r="D9" s="114">
+        <v>12</v>
+      </c>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
       <c r="G9" s="78"/>
       <c r="H9" s="79"/>
       <c r="I9" s="80">
         <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K9" s="51"/>
       <c r="L9" s="121"/>
@@ -6986,7 +6998,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -7021,7 +7033,9 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>91</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
@@ -7029,7 +7043,7 @@
       <c r="H10" s="73"/>
       <c r="I10" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -7061,7 +7075,7 @@
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2184</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -7096,7 +7110,9 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>46</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
@@ -7104,7 +7120,7 @@
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
@@ -7136,7 +7152,7 @@
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1104</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -7171,19 +7187,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>9</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -7211,7 +7231,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -7246,47 +7266,65 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
+      <c r="C13" s="113">
+        <v>3393</v>
+      </c>
       <c r="D13" s="114"/>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>26</v>
+      </c>
+      <c r="H13" s="79">
+        <v>35</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3367</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-35</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
+      <c r="L13" s="121">
+        <v>9</v>
+      </c>
+      <c r="M13" s="121">
+        <v>10</v>
+      </c>
+      <c r="N13" s="121">
+        <v>10</v>
+      </c>
+      <c r="O13" s="121">
+        <v>13</v>
+      </c>
+      <c r="P13" s="121">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>12</v>
+      </c>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>624</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>80773</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -7328,19 +7366,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" ref="J14:J59" si="7">D14-H14</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -7368,7 +7410,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -7403,7 +7445,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>2</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -7411,7 +7455,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="7"/>
@@ -7443,7 +7487,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -7628,7 +7672,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -7636,7 +7682,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="7"/>
@@ -7668,7 +7714,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -7778,19 +7824,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -7818,7 +7868,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -7853,7 +7903,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -7861,7 +7913,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="7"/>
@@ -7893,7 +7945,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -7928,7 +7980,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -7936,7 +7990,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="7"/>
@@ -7968,7 +8022,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -8003,19 +8057,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -8043,7 +8101,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -8085,19 +8143,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -8125,7 +8187,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -8167,7 +8229,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>5</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -8175,7 +8239,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="7"/>
@@ -8207,7 +8271,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -8242,30 +8306,38 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>55</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
-      <c r="G26" s="76"/>
+      <c r="G26" s="76">
+        <v>2</v>
+      </c>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
       <c r="M26" s="112"/>
       <c r="N26" s="112"/>
       <c r="O26" s="112"/>
-      <c r="P26" s="112"/>
+      <c r="P26" s="112">
+        <v>2</v>
+      </c>
       <c r="Q26" s="120"/>
       <c r="R26" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" s="124">
         <f t="shared" si="8"/>
@@ -8274,15 +8346,15 @@
       <c r="T26" s="41"/>
       <c r="U26" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V26" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1273</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -8298,7 +8370,9 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="110"/>
+      <c r="C27" s="110">
+        <v>5</v>
+      </c>
       <c r="D27" s="111"/>
       <c r="E27" s="112"/>
       <c r="F27" s="112"/>
@@ -8306,7 +8380,7 @@
       <c r="H27" s="73"/>
       <c r="I27" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J27" s="77">
         <f t="shared" si="7"/>
@@ -8338,7 +8412,7 @@
       </c>
       <c r="W27" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X27" s="27"/>
       <c r="Y27" s="2"/>
@@ -8357,7 +8431,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>3</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -8365,7 +8441,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="7"/>
@@ -8397,7 +8473,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -8416,11 +8492,15 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>3</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
+      <c r="G29" s="76">
+        <v>3</v>
+      </c>
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
@@ -8435,11 +8515,13 @@
       <c r="M29" s="112"/>
       <c r="N29" s="112"/>
       <c r="O29" s="112"/>
-      <c r="P29" s="112"/>
+      <c r="P29" s="112">
+        <v>3</v>
+      </c>
       <c r="Q29" s="120"/>
       <c r="R29" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S29" s="124">
         <f t="shared" si="8"/>
@@ -8448,11 +8530,11 @@
       <c r="T29" s="42"/>
       <c r="U29" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V29" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W29" s="129">
         <f t="shared" si="9"/>
@@ -8475,30 +8557,38 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>28</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
-      <c r="G30" s="76"/>
+      <c r="G30" s="76">
+        <v>1</v>
+      </c>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
       <c r="M30" s="112"/>
       <c r="N30" s="112"/>
       <c r="O30" s="112"/>
-      <c r="P30" s="112"/>
+      <c r="P30" s="112">
+        <v>1</v>
+      </c>
       <c r="Q30" s="120"/>
       <c r="R30" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" s="124">
         <f t="shared" si="8"/>
@@ -8507,15 +8597,15 @@
       <c r="T30" s="41"/>
       <c r="U30" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V30" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>653</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -8527,15 +8617,19 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>15</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
-      <c r="G31" s="76"/>
+      <c r="G31" s="76">
+        <v>1</v>
+      </c>
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="7"/>
@@ -8546,11 +8640,13 @@
       <c r="M31" s="112"/>
       <c r="N31" s="112"/>
       <c r="O31" s="112"/>
-      <c r="P31" s="112"/>
+      <c r="P31" s="112">
+        <v>1</v>
+      </c>
       <c r="Q31" s="120"/>
       <c r="R31" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="124">
         <f t="shared" si="8"/>
@@ -8559,15 +8655,15 @@
       <c r="T31" s="41"/>
       <c r="U31" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V31" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -8579,7 +8675,9 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="110"/>
+      <c r="C32" s="110">
+        <v>2</v>
+      </c>
       <c r="D32" s="111"/>
       <c r="E32" s="112"/>
       <c r="F32" s="112"/>
@@ -8587,7 +8685,7 @@
       <c r="H32" s="73"/>
       <c r="I32" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" s="77">
         <f t="shared" si="7"/>
@@ -8619,7 +8717,7 @@
       </c>
       <c r="W32" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X32" s="27"/>
     </row>
@@ -8683,7 +8781,9 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>2</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
@@ -8691,7 +8791,7 @@
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" s="77">
         <f t="shared" si="7"/>
@@ -8723,7 +8823,7 @@
       </c>
       <c r="W34" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -8735,19 +8835,23 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>194</v>
+      </c>
+      <c r="D35" s="111">
+        <v>2</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
       <c r="G35" s="76"/>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="112"/>
@@ -8775,7 +8879,7 @@
       </c>
       <c r="W35" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>4658</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -8891,47 +8995,59 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>3457</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>93</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3364</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
-      <c r="M38" s="121"/>
+      <c r="L38" s="121">
+        <v>32</v>
+      </c>
+      <c r="M38" s="121">
+        <v>10</v>
+      </c>
       <c r="N38" s="121"/>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>51</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>498</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>20185</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -8943,7 +9059,9 @@
       <c r="B39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="110"/>
+      <c r="C39" s="110">
+        <v>5</v>
+      </c>
       <c r="D39" s="111"/>
       <c r="E39" s="112"/>
       <c r="F39" s="112"/>
@@ -8951,7 +9069,7 @@
       <c r="H39" s="73"/>
       <c r="I39" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J39" s="77">
         <f t="shared" si="7"/>
@@ -8983,7 +9101,7 @@
       </c>
       <c r="W39" s="129">
         <f t="shared" ref="W39:W41" si="11">I39*24+J39</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X39" s="27"/>
     </row>
@@ -9047,30 +9165,38 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>370</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
-      <c r="G41" s="149"/>
+      <c r="G41" s="149">
+        <v>2</v>
+      </c>
       <c r="H41" s="150"/>
       <c r="I41" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>368</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="153"/>
       <c r="L41" s="154"/>
       <c r="M41" s="154"/>
       <c r="N41" s="154"/>
       <c r="O41" s="154"/>
-      <c r="P41" s="154"/>
+      <c r="P41" s="154">
+        <v>2</v>
+      </c>
       <c r="Q41" s="155"/>
       <c r="R41" s="156">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S41" s="157">
         <f t="shared" si="8"/>
@@ -9079,15 +9205,15 @@
       <c r="T41" s="153"/>
       <c r="U41" s="158">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V41" s="159">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W41" s="159">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>8852</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -9099,22 +9225,28 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>576</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>10</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="181">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>566</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K42" s="169"/>
-      <c r="L42" s="165"/>
+      <c r="L42" s="165">
+        <v>10</v>
+      </c>
       <c r="M42" s="165"/>
       <c r="N42" s="165"/>
       <c r="O42" s="165"/>
@@ -9122,7 +9254,7 @@
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="8"/>
@@ -9131,15 +9263,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>6792</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -9194,30 +9326,42 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>39567</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>1286</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="182">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>38281</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>632</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>362</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>292</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1286</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="8"/>
@@ -9226,15 +9370,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>7716</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>1286</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>229689</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -9290,7 +9434,9 @@
       <c r="B46" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="110"/>
+      <c r="C46" s="110">
+        <v>5</v>
+      </c>
       <c r="D46" s="111"/>
       <c r="E46" s="112"/>
       <c r="F46" s="112"/>
@@ -9298,7 +9444,7 @@
       <c r="H46" s="73"/>
       <c r="I46" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J46" s="77">
         <f t="shared" si="7"/>
@@ -9330,7 +9476,7 @@
       </c>
       <c r="W46" s="129">
         <f t="shared" ref="W46:W47" si="14">I46*24+J46</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X46" s="27"/>
     </row>
@@ -9394,22 +9540,30 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2696</v>
+      </c>
+      <c r="D48" s="142">
+        <v>3</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
-      <c r="G48" s="143"/>
+      <c r="G48" s="143">
+        <v>5</v>
+      </c>
       <c r="H48" s="139"/>
       <c r="I48" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2691</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48" s="51"/>
-      <c r="L48" s="121"/>
+      <c r="L48" s="121">
+        <v>5</v>
+      </c>
       <c r="M48" s="121"/>
       <c r="N48" s="121"/>
       <c r="O48" s="121"/>
@@ -9417,7 +9571,7 @@
       <c r="Q48" s="122"/>
       <c r="R48" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S48" s="144">
         <f t="shared" si="8"/>
@@ -9426,15 +9580,15 @@
       <c r="T48" s="51"/>
       <c r="U48" s="131">
         <f>L48*6+N48*6+P48*6</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V48" s="135">
         <f>U48/6</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16149</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -9446,7 +9600,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -9454,7 +9610,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="7"/>
@@ -9486,7 +9642,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -9498,7 +9654,9 @@
       <c r="B50" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="110"/>
+      <c r="C50" s="110">
+        <v>10</v>
+      </c>
       <c r="D50" s="111"/>
       <c r="E50" s="112"/>
       <c r="F50" s="112"/>
@@ -9506,7 +9664,7 @@
       <c r="H50" s="73"/>
       <c r="I50" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J50" s="77">
         <f t="shared" si="7"/>
@@ -9538,7 +9696,7 @@
       </c>
       <c r="W50" s="129">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X50" s="27"/>
     </row>
@@ -9602,7 +9760,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -9610,7 +9770,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="78">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="7"/>
@@ -9642,7 +9802,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -9707,7 +9867,7 @@
         <v>78</v>
       </c>
       <c r="C54" s="110">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
@@ -9716,7 +9876,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="7"/>
@@ -9748,7 +9908,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="20"/>
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -9963,11 +10123,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>9</v>
+        <v>50756</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -9976,65 +10136,65 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1430</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>9</v>
+        <v>49326</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>688</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R60" s="85">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1420</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>9228</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
+        <v>1420</v>
       </c>
       <c r="W60" s="180">
         <f>SUM(W8:W59)</f>
-        <v>216</v>
+        <v>378470</v>
       </c>
       <c r="X60" s="45"/>
     </row>

--- a/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A96BD5D-CB2B-45AA-A4E5-8368E9169654}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8960B0A5-8630-4E39-BAEF-1F15550CF5C3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -10936,19 +10936,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>33</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8+E8-G8</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -10976,7 +10980,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -11011,19 +11015,23 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
-      <c r="D9" s="114"/>
+      <c r="C9" s="113">
+        <v>87</v>
+      </c>
+      <c r="D9" s="114">
+        <v>12</v>
+      </c>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
       <c r="G9" s="78"/>
       <c r="H9" s="79"/>
       <c r="I9" s="80">
         <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K9" s="51"/>
       <c r="L9" s="121"/>
@@ -11051,7 +11059,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -11086,7 +11094,9 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>91</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
@@ -11094,7 +11104,7 @@
       <c r="H10" s="73"/>
       <c r="I10" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -11126,7 +11136,7 @@
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2184</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -11161,15 +11171,19 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>46</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
-      <c r="G11" s="76"/>
+      <c r="G11" s="76">
+        <v>2</v>
+      </c>
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
@@ -11180,11 +11194,13 @@
       <c r="M11" s="112"/>
       <c r="N11" s="112"/>
       <c r="O11" s="112"/>
-      <c r="P11" s="112"/>
+      <c r="P11" s="112">
+        <v>2</v>
+      </c>
       <c r="Q11" s="120"/>
       <c r="R11" s="86">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" s="124">
         <f t="shared" si="1"/>
@@ -11193,15 +11209,15 @@
       <c r="T11" s="41"/>
       <c r="U11" s="107">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V11" s="130">
         <f>U11/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -11236,19 +11252,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>9</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -11276,7 +11296,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -11311,47 +11331,65 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3365</v>
+      </c>
+      <c r="D13" s="114">
+        <v>13</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>27</v>
+      </c>
+      <c r="H13" s="79">
+        <v>12</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3338</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
+      <c r="L13" s="121">
+        <v>3</v>
+      </c>
       <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
+      <c r="N13" s="121">
+        <v>8</v>
+      </c>
+      <c r="O13" s="121">
+        <v>10</v>
+      </c>
+      <c r="P13" s="121">
+        <v>16</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>2</v>
+      </c>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>80113</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -11393,19 +11431,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" ref="J14:J59" si="7">D14-H14</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -11433,7 +11475,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -11468,7 +11510,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>2</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -11476,7 +11520,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="7"/>
@@ -11508,7 +11552,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -11693,7 +11737,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -11701,7 +11747,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="7"/>
@@ -11733,7 +11779,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -11843,19 +11889,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -11883,7 +11933,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -11918,7 +11968,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -11926,7 +11978,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="7"/>
@@ -11958,7 +12010,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -11993,7 +12045,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -12001,7 +12055,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="7"/>
@@ -12033,7 +12087,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -12068,19 +12122,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -12108,7 +12166,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -12150,19 +12208,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -12190,7 +12252,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -12232,7 +12294,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>5</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -12240,7 +12304,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="7"/>
@@ -12272,7 +12336,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -12307,30 +12371,40 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>53</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
-      <c r="G26" s="76"/>
+      <c r="G26" s="76">
+        <v>4</v>
+      </c>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
-      <c r="L26" s="112"/>
+      <c r="L26" s="112">
+        <v>2</v>
+      </c>
       <c r="M26" s="112"/>
       <c r="N26" s="112"/>
       <c r="O26" s="112"/>
-      <c r="P26" s="112"/>
+      <c r="P26" s="112">
+        <v>2</v>
+      </c>
       <c r="Q26" s="120"/>
       <c r="R26" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S26" s="124">
         <f t="shared" si="8"/>
@@ -12339,15 +12413,15 @@
       <c r="T26" s="41"/>
       <c r="U26" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V26" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W26" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1177</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -12363,7 +12437,9 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="110"/>
+      <c r="C27" s="110">
+        <v>5</v>
+      </c>
       <c r="D27" s="111"/>
       <c r="E27" s="112"/>
       <c r="F27" s="112"/>
@@ -12371,7 +12447,7 @@
       <c r="H27" s="73"/>
       <c r="I27" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J27" s="77">
         <f t="shared" si="7"/>
@@ -12403,7 +12479,7 @@
       </c>
       <c r="W27" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X27" s="27"/>
       <c r="Y27" s="2"/>
@@ -12422,7 +12498,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>3</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -12430,7 +12508,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="7"/>
@@ -12462,7 +12540,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -12540,22 +12618,30 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>27</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
-      <c r="G30" s="76"/>
+      <c r="G30" s="76">
+        <v>1</v>
+      </c>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
-      <c r="L30" s="112"/>
+      <c r="L30" s="112">
+        <v>1</v>
+      </c>
       <c r="M30" s="112"/>
       <c r="N30" s="112"/>
       <c r="O30" s="112"/>
@@ -12563,7 +12649,7 @@
       <c r="Q30" s="120"/>
       <c r="R30" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" s="124">
         <f t="shared" si="8"/>
@@ -12572,15 +12658,15 @@
       <c r="T30" s="41"/>
       <c r="U30" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V30" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>629</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -12592,22 +12678,28 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>14</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
-      <c r="G31" s="76"/>
+      <c r="G31" s="76">
+        <v>2</v>
+      </c>
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K31" s="41"/>
-      <c r="L31" s="112"/>
+      <c r="L31" s="112">
+        <v>2</v>
+      </c>
       <c r="M31" s="112"/>
       <c r="N31" s="112"/>
       <c r="O31" s="112"/>
@@ -12615,7 +12707,7 @@
       <c r="Q31" s="120"/>
       <c r="R31" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S31" s="124">
         <f t="shared" si="8"/>
@@ -12624,15 +12716,15 @@
       <c r="T31" s="41"/>
       <c r="U31" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V31" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W31" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -12644,15 +12736,19 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="110"/>
+      <c r="C32" s="110">
+        <v>2</v>
+      </c>
       <c r="D32" s="111"/>
       <c r="E32" s="112"/>
       <c r="F32" s="112"/>
-      <c r="G32" s="76"/>
+      <c r="G32" s="76">
+        <v>1</v>
+      </c>
       <c r="H32" s="73"/>
       <c r="I32" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="77">
         <f t="shared" si="7"/>
@@ -12663,11 +12759,13 @@
       <c r="M32" s="112"/>
       <c r="N32" s="112"/>
       <c r="O32" s="112"/>
-      <c r="P32" s="112"/>
+      <c r="P32" s="112">
+        <v>1</v>
+      </c>
       <c r="Q32" s="120"/>
       <c r="R32" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="124">
         <f t="shared" si="8"/>
@@ -12676,15 +12774,15 @@
       <c r="T32" s="41"/>
       <c r="U32" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V32" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X32" s="27"/>
     </row>
@@ -12748,7 +12846,9 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>2</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
@@ -12756,7 +12856,7 @@
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" s="77">
         <f t="shared" si="7"/>
@@ -12788,7 +12888,7 @@
       </c>
       <c r="W34" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -12800,30 +12900,40 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>194</v>
+      </c>
+      <c r="D35" s="111">
+        <v>2</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
-      <c r="G35" s="76"/>
+      <c r="G35" s="76">
+        <v>4</v>
+      </c>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" s="41"/>
-      <c r="L35" s="112"/>
+      <c r="L35" s="112">
+        <v>3</v>
+      </c>
       <c r="M35" s="112"/>
-      <c r="N35" s="112"/>
+      <c r="N35" s="112">
+        <v>1</v>
+      </c>
       <c r="O35" s="112"/>
       <c r="P35" s="112"/>
       <c r="Q35" s="120"/>
       <c r="R35" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S35" s="124">
         <f t="shared" si="8"/>
@@ -12832,15 +12942,15 @@
       <c r="T35" s="41"/>
       <c r="U35" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V35" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W35" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>4562</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -12956,30 +13066,42 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>3364</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>154</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3210</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
+      <c r="L38" s="121">
+        <v>20</v>
+      </c>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>26</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>108</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="8"/>
@@ -12988,15 +13110,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>924</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>19261</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -13008,15 +13130,19 @@
       <c r="B39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="110"/>
+      <c r="C39" s="110">
+        <v>5</v>
+      </c>
       <c r="D39" s="111"/>
       <c r="E39" s="112"/>
       <c r="F39" s="112"/>
-      <c r="G39" s="76"/>
+      <c r="G39" s="76">
+        <v>1</v>
+      </c>
       <c r="H39" s="73"/>
       <c r="I39" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J39" s="77">
         <f t="shared" si="7"/>
@@ -13027,11 +13153,13 @@
       <c r="M39" s="112"/>
       <c r="N39" s="112"/>
       <c r="O39" s="112"/>
-      <c r="P39" s="112"/>
+      <c r="P39" s="112">
+        <v>1</v>
+      </c>
       <c r="Q39" s="120"/>
       <c r="R39" s="96">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" s="126">
         <f t="shared" si="8"/>
@@ -13040,15 +13168,15 @@
       <c r="T39" s="41"/>
       <c r="U39" s="107">
         <f t="shared" ref="U39:U41" si="10">L39*24+N39*24+P39*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V39" s="109">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W39" s="129">
         <f t="shared" ref="W39:W41" si="11">I39*24+J39</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X39" s="27"/>
     </row>
@@ -13112,22 +13240,30 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>368</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
-      <c r="G41" s="149"/>
+      <c r="G41" s="149">
+        <v>55</v>
+      </c>
       <c r="H41" s="150"/>
       <c r="I41" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="153"/>
-      <c r="L41" s="154"/>
+      <c r="L41" s="154">
+        <v>55</v>
+      </c>
       <c r="M41" s="154"/>
       <c r="N41" s="154"/>
       <c r="O41" s="154"/>
@@ -13135,7 +13271,7 @@
       <c r="Q41" s="155"/>
       <c r="R41" s="156">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="S41" s="157">
         <f t="shared" si="8"/>
@@ -13144,15 +13280,15 @@
       <c r="T41" s="153"/>
       <c r="U41" s="158">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1320</v>
       </c>
       <c r="V41" s="159">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="W41" s="159">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>7532</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -13164,30 +13300,40 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>566</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>30</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="181">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>536</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K42" s="169"/>
-      <c r="L42" s="165"/>
+      <c r="L42" s="165">
+        <v>8</v>
+      </c>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>10</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>12</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="8"/>
@@ -13196,15 +13342,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>6432</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -13259,30 +13405,42 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>38281</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>1061</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="182">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37220</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>347</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>345</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>369</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1061</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="8"/>
@@ -13291,15 +13449,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>6366</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>1061</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>223323</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -13355,7 +13513,9 @@
       <c r="B46" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="110"/>
+      <c r="C46" s="110">
+        <v>5</v>
+      </c>
       <c r="D46" s="111"/>
       <c r="E46" s="112"/>
       <c r="F46" s="112"/>
@@ -13363,7 +13523,7 @@
       <c r="H46" s="73"/>
       <c r="I46" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J46" s="77">
         <f t="shared" si="7"/>
@@ -13395,7 +13555,7 @@
       </c>
       <c r="W46" s="129">
         <f t="shared" ref="W46:W47" si="14">I46*24+J46</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X46" s="27"/>
     </row>
@@ -13459,19 +13619,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2691</v>
+      </c>
+      <c r="D48" s="142">
+        <v>3</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
       <c r="G48" s="143"/>
       <c r="H48" s="139"/>
       <c r="I48" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2691</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
@@ -13499,7 +13663,7 @@
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16149</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -13511,7 +13675,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -13519,7 +13685,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="7"/>
@@ -13551,7 +13717,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -13563,11 +13729,15 @@
       <c r="B50" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="110"/>
+      <c r="C50" s="110">
+        <v>10</v>
+      </c>
       <c r="D50" s="111"/>
       <c r="E50" s="112"/>
       <c r="F50" s="112"/>
-      <c r="G50" s="76"/>
+      <c r="G50" s="76">
+        <v>10</v>
+      </c>
       <c r="H50" s="73"/>
       <c r="I50" s="73">
         <f t="shared" si="4"/>
@@ -13582,11 +13752,13 @@
       <c r="M50" s="112"/>
       <c r="N50" s="112"/>
       <c r="O50" s="112"/>
-      <c r="P50" s="112"/>
+      <c r="P50" s="112">
+        <v>10</v>
+      </c>
       <c r="Q50" s="120"/>
       <c r="R50" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S50" s="124">
         <f t="shared" si="8"/>
@@ -13595,11 +13767,11 @@
       <c r="T50" s="41"/>
       <c r="U50" s="107">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V50" s="130">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W50" s="129">
         <f t="shared" si="17"/>
@@ -13667,7 +13839,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -13675,7 +13849,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="78">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="7"/>
@@ -13707,7 +13881,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -13772,7 +13946,7 @@
         <v>78</v>
       </c>
       <c r="C54" s="110">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
@@ -13781,7 +13955,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="7"/>
@@ -13813,7 +13987,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="20"/>
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -14028,11 +14202,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>9</v>
+        <v>49324</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -14041,24 +14215,24 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>9</v>
+        <v>47972</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="21"/>
@@ -14066,40 +14240,40 @@
       </c>
       <c r="N60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>521</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R60" s="85">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>10218</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="W60" s="180">
         <f>SUM(W8:W59)</f>
-        <v>216</v>
+        <v>368240</v>
       </c>
       <c r="X60" s="45"/>
     </row>

--- a/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8960B0A5-8630-4E39-BAEF-1F15550CF5C3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A435720-6C7E-4548-8C6D-CE054B6A3D1B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -15015,19 +15015,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>33</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8+E8-G8</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -15055,7 +15059,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -15090,22 +15094,30 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
-      <c r="D9" s="114"/>
+      <c r="C9" s="113">
+        <v>87</v>
+      </c>
+      <c r="D9" s="114">
+        <v>12</v>
+      </c>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
-      <c r="G9" s="78"/>
+      <c r="G9" s="78">
+        <v>1</v>
+      </c>
       <c r="H9" s="79"/>
       <c r="I9" s="80">
         <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K9" s="51"/>
-      <c r="L9" s="121"/>
+      <c r="L9" s="121">
+        <v>1</v>
+      </c>
       <c r="M9" s="121"/>
       <c r="N9" s="121"/>
       <c r="O9" s="121"/>
@@ -15113,7 +15125,7 @@
       <c r="Q9" s="122"/>
       <c r="R9" s="98">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="125">
         <f t="shared" si="1"/>
@@ -15122,15 +15134,15 @@
       <c r="T9" s="51"/>
       <c r="U9" s="131">
         <f>L9*24+N9*24+P9*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V9" s="132">
         <f>U9/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2076</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -15165,7 +15177,9 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>91</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
@@ -15173,7 +15187,7 @@
       <c r="H10" s="73"/>
       <c r="I10" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -15205,7 +15219,7 @@
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2184</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -15240,30 +15254,38 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>44</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
-      <c r="G11" s="76"/>
+      <c r="G11" s="76">
+        <v>3</v>
+      </c>
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11" s="41"/>
-      <c r="L11" s="112"/>
+      <c r="L11" s="112">
+        <v>2</v>
+      </c>
       <c r="M11" s="112"/>
       <c r="N11" s="112"/>
       <c r="O11" s="112"/>
-      <c r="P11" s="112"/>
+      <c r="P11" s="112">
+        <v>1</v>
+      </c>
       <c r="Q11" s="120"/>
       <c r="R11" s="86">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" s="124">
         <f t="shared" si="1"/>
@@ -15272,15 +15294,15 @@
       <c r="T11" s="41"/>
       <c r="U11" s="107">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V11" s="130">
         <f>U11/24</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>984</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -15315,19 +15337,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>9</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -15355,7 +15381,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -15390,47 +15416,67 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3338</v>
+      </c>
+      <c r="D13" s="114">
+        <v>1</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>28</v>
+      </c>
+      <c r="H13" s="79">
+        <v>22</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3310</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
+      <c r="L13" s="121">
+        <v>2</v>
+      </c>
+      <c r="M13" s="121">
+        <v>15</v>
+      </c>
+      <c r="N13" s="121">
+        <v>9</v>
+      </c>
+      <c r="O13" s="121">
+        <v>2</v>
+      </c>
+      <c r="P13" s="121">
+        <v>17</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>5</v>
+      </c>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>672</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>79419</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -15472,19 +15518,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" ref="J14:J59" si="7">D14-H14</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -15512,7 +15562,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -15547,7 +15597,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>2</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -15555,7 +15607,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="7"/>
@@ -15587,7 +15639,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -15772,7 +15824,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -15780,7 +15834,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="7"/>
@@ -15812,7 +15866,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -15922,19 +15976,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -15962,7 +16020,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -15997,7 +16055,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -16005,7 +16065,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="7"/>
@@ -16037,7 +16097,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -16072,7 +16132,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -16080,7 +16142,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="7"/>
@@ -16112,7 +16174,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -16147,19 +16209,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -16187,7 +16253,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -16229,19 +16295,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -16269,7 +16339,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -16311,7 +16381,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>5</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -16319,7 +16391,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="7"/>
@@ -16351,7 +16423,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -16386,19 +16458,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>49</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
       <c r="G26" s="76"/>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
@@ -16426,7 +16502,7 @@
       </c>
       <c r="W26" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1177</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -16442,15 +16518,19 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="110"/>
+      <c r="C27" s="110">
+        <v>5</v>
+      </c>
       <c r="D27" s="111"/>
       <c r="E27" s="112"/>
       <c r="F27" s="112"/>
-      <c r="G27" s="76"/>
+      <c r="G27" s="76">
+        <v>3</v>
+      </c>
       <c r="H27" s="73"/>
       <c r="I27" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" s="77">
         <f t="shared" si="7"/>
@@ -16461,11 +16541,13 @@
       <c r="M27" s="112"/>
       <c r="N27" s="112"/>
       <c r="O27" s="112"/>
-      <c r="P27" s="112"/>
+      <c r="P27" s="112">
+        <v>3</v>
+      </c>
       <c r="Q27" s="120"/>
       <c r="R27" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S27" s="124">
         <f t="shared" si="8"/>
@@ -16474,15 +16556,15 @@
       <c r="T27" s="42"/>
       <c r="U27" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V27" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W27" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X27" s="27"/>
       <c r="Y27" s="2"/>
@@ -16501,7 +16583,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>3</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -16509,7 +16593,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="7"/>
@@ -16541,7 +16625,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -16619,19 +16703,23 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>26</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
       <c r="G30" s="76"/>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
@@ -16659,7 +16747,7 @@
       </c>
       <c r="W30" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>629</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -16671,7 +16759,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>12</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
@@ -16679,7 +16769,7 @@
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="7"/>
@@ -16711,7 +16801,7 @@
       </c>
       <c r="W31" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -16723,11 +16813,15 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="110"/>
+      <c r="C32" s="110">
+        <v>1</v>
+      </c>
       <c r="D32" s="111"/>
       <c r="E32" s="112"/>
       <c r="F32" s="112"/>
-      <c r="G32" s="76"/>
+      <c r="G32" s="76">
+        <v>1</v>
+      </c>
       <c r="H32" s="73"/>
       <c r="I32" s="73">
         <f t="shared" si="4"/>
@@ -16738,7 +16832,9 @@
         <v>0</v>
       </c>
       <c r="K32" s="41"/>
-      <c r="L32" s="112"/>
+      <c r="L32" s="112">
+        <v>1</v>
+      </c>
       <c r="M32" s="112"/>
       <c r="N32" s="112"/>
       <c r="O32" s="112"/>
@@ -16746,7 +16842,7 @@
       <c r="Q32" s="120"/>
       <c r="R32" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="124">
         <f t="shared" si="8"/>
@@ -16755,11 +16851,11 @@
       <c r="T32" s="41"/>
       <c r="U32" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V32" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" s="129">
         <f t="shared" si="9"/>
@@ -16827,7 +16923,9 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>2</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
@@ -16835,7 +16933,7 @@
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" s="77">
         <f t="shared" si="7"/>
@@ -16867,7 +16965,7 @@
       </c>
       <c r="W34" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -16879,30 +16977,38 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>190</v>
+      </c>
+      <c r="D35" s="111">
+        <v>2</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
-      <c r="G35" s="76"/>
+      <c r="G35" s="76">
+        <v>1</v>
+      </c>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="112"/>
       <c r="M35" s="112"/>
       <c r="N35" s="112"/>
       <c r="O35" s="112"/>
-      <c r="P35" s="112"/>
+      <c r="P35" s="112">
+        <v>1</v>
+      </c>
       <c r="Q35" s="120"/>
       <c r="R35" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" s="124">
         <f t="shared" si="8"/>
@@ -16911,15 +17017,15 @@
       <c r="T35" s="41"/>
       <c r="U35" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V35" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>4538</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -17035,30 +17141,42 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>3210</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>104</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3106</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
+      <c r="L38" s="121">
+        <v>14</v>
+      </c>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>10</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>80</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="8"/>
@@ -17067,15 +17185,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>624</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>18637</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -17087,15 +17205,19 @@
       <c r="B39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="110"/>
+      <c r="C39" s="110">
+        <v>4</v>
+      </c>
       <c r="D39" s="111"/>
       <c r="E39" s="112"/>
       <c r="F39" s="112"/>
-      <c r="G39" s="76"/>
+      <c r="G39" s="76">
+        <v>3</v>
+      </c>
       <c r="H39" s="73"/>
       <c r="I39" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="77">
         <f t="shared" si="7"/>
@@ -17106,11 +17228,13 @@
       <c r="M39" s="112"/>
       <c r="N39" s="112"/>
       <c r="O39" s="112"/>
-      <c r="P39" s="112"/>
+      <c r="P39" s="112">
+        <v>3</v>
+      </c>
       <c r="Q39" s="120"/>
       <c r="R39" s="96">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S39" s="126">
         <f t="shared" si="8"/>
@@ -17119,15 +17243,15 @@
       <c r="T39" s="41"/>
       <c r="U39" s="107">
         <f t="shared" ref="U39:U41" si="10">L39*24+N39*24+P39*24</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V39" s="109">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W39" s="129">
         <f t="shared" ref="W39:W41" si="11">I39*24+J39</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X39" s="27"/>
     </row>
@@ -17191,30 +17315,38 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>313</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
-      <c r="G41" s="149"/>
+      <c r="G41" s="149">
+        <v>1</v>
+      </c>
       <c r="H41" s="150"/>
       <c r="I41" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="153"/>
       <c r="L41" s="154"/>
       <c r="M41" s="154"/>
       <c r="N41" s="154"/>
       <c r="O41" s="154"/>
-      <c r="P41" s="154"/>
+      <c r="P41" s="154">
+        <v>1</v>
+      </c>
       <c r="Q41" s="155"/>
       <c r="R41" s="156">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" s="157">
         <f t="shared" si="8"/>
@@ -17223,15 +17355,15 @@
       <c r="T41" s="153"/>
       <c r="U41" s="158">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V41" s="159">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="159">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>7508</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -17243,30 +17375,40 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>536</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>37</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="181">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K42" s="169"/>
-      <c r="L42" s="165"/>
+      <c r="L42" s="165">
+        <v>10</v>
+      </c>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>2</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>25</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="8"/>
@@ -17275,15 +17417,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>5988</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -17338,30 +17480,42 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>37220</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>1206</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="182">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>36014</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>412</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>288</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>506</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1206</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="8"/>
@@ -17370,15 +17524,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>7236</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>1206</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>216087</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -17434,30 +17588,38 @@
       <c r="B46" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="110"/>
+      <c r="C46" s="110">
+        <v>5</v>
+      </c>
       <c r="D46" s="111"/>
       <c r="E46" s="112"/>
       <c r="F46" s="112"/>
-      <c r="G46" s="76"/>
+      <c r="G46" s="76">
+        <v>4</v>
+      </c>
       <c r="H46" s="73"/>
       <c r="I46" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="77">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K46" s="41"/>
-      <c r="L46" s="112"/>
+      <c r="L46" s="112">
+        <v>1</v>
+      </c>
       <c r="M46" s="112"/>
       <c r="N46" s="112"/>
       <c r="O46" s="112"/>
-      <c r="P46" s="112"/>
+      <c r="P46" s="112">
+        <v>3</v>
+      </c>
       <c r="Q46" s="120"/>
       <c r="R46" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S46" s="128">
         <f t="shared" si="8"/>
@@ -17466,15 +17628,15 @@
       <c r="T46" s="41"/>
       <c r="U46" s="107">
         <f t="shared" ref="U46:U47" si="12">L46*24+N46*24+P46*24</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V46" s="134">
         <f t="shared" ref="V46:V47" si="13">U46/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W46" s="129">
         <f t="shared" ref="W46:W47" si="14">I46*24+J46</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X46" s="27"/>
     </row>
@@ -17538,22 +17700,30 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2691</v>
+      </c>
+      <c r="D48" s="142">
+        <v>3</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
-      <c r="G48" s="143"/>
+      <c r="G48" s="143">
+        <v>5</v>
+      </c>
       <c r="H48" s="139"/>
       <c r="I48" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2686</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48" s="51"/>
-      <c r="L48" s="121"/>
+      <c r="L48" s="121">
+        <v>5</v>
+      </c>
       <c r="M48" s="121"/>
       <c r="N48" s="121"/>
       <c r="O48" s="121"/>
@@ -17561,7 +17731,7 @@
       <c r="Q48" s="122"/>
       <c r="R48" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S48" s="144">
         <f t="shared" si="8"/>
@@ -17570,15 +17740,15 @@
       <c r="T48" s="51"/>
       <c r="U48" s="131">
         <f>L48*6+N48*6+P48*6</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V48" s="135">
         <f>U48/6</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16119</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -17590,7 +17760,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -17598,7 +17770,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="7"/>
@@ -17630,7 +17802,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -17746,7 +17918,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -17754,7 +17928,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="78">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="7"/>
@@ -17786,7 +17960,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -17851,7 +18025,7 @@
         <v>78</v>
       </c>
       <c r="C54" s="110">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
@@ -17860,7 +18034,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="7"/>
@@ -17892,7 +18066,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="20"/>
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -18107,11 +18281,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>9</v>
+        <v>47972</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -18120,65 +18294,65 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1397</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>9</v>
+        <v>46575</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>309</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R60" s="85">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1397</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>9414</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
+        <v>1397</v>
       </c>
       <c r="W60" s="180">
         <f>SUM(W8:W59)</f>
-        <v>216</v>
+        <v>358804</v>
       </c>
       <c r="X60" s="45"/>
     </row>

--- a/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344F4625-0E4C-4445-81F8-73A9E8F2C34D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61981DC6-CC54-4792-A4F3-FB97B75D9D3C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -25,8 +25,8 @@
     <sheet name="08,12" sheetId="140" r:id="rId10"/>
     <sheet name="08,13" sheetId="141" r:id="rId11"/>
     <sheet name="08,14" sheetId="142" r:id="rId12"/>
-    <sheet name="08,15 (2)" sheetId="144" r:id="rId13"/>
-    <sheet name="08,15 (3)" sheetId="145" r:id="rId14"/>
+    <sheet name="08,15" sheetId="144" r:id="rId13"/>
+    <sheet name="08,17" sheetId="145" r:id="rId14"/>
     <sheet name="08,15 (4)" sheetId="146" r:id="rId15"/>
     <sheet name="08,15 (5)" sheetId="147" r:id="rId16"/>
   </sheets>
@@ -42,10 +42,10 @@
     <definedName name="_xlnm.Print_Area" localSheetId="9">'08,12'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'08,13'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'08,14'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'08,15 (2)'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="13">'08,15 (3)'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'08,15'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'08,15 (4)'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'08,15 (5)'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'08,17'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -23150,7 +23150,7 @@
         <v>1</v>
       </c>
       <c r="P1" s="200">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="Q1" s="201"/>
       <c r="R1" s="201"/>
@@ -23404,19 +23404,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>33</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8+E8-G8</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -23444,7 +23448,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -23479,22 +23483,30 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
-      <c r="D9" s="114"/>
+      <c r="C9" s="113">
+        <v>85</v>
+      </c>
+      <c r="D9" s="114">
+        <v>12</v>
+      </c>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
-      <c r="G9" s="78"/>
+      <c r="G9" s="78">
+        <v>5</v>
+      </c>
       <c r="H9" s="79"/>
       <c r="I9" s="80">
         <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K9" s="51"/>
-      <c r="L9" s="121"/>
+      <c r="L9" s="121">
+        <v>5</v>
+      </c>
       <c r="M9" s="121"/>
       <c r="N9" s="121"/>
       <c r="O9" s="121"/>
@@ -23502,7 +23514,7 @@
       <c r="Q9" s="122"/>
       <c r="R9" s="98">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S9" s="125">
         <f t="shared" si="1"/>
@@ -23511,15 +23523,15 @@
       <c r="T9" s="51"/>
       <c r="U9" s="131">
         <f>L9*24+N9*24+P9*24</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V9" s="132">
         <f>U9/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1932</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -23554,30 +23566,38 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>90</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
-      <c r="G10" s="76"/>
+      <c r="G10" s="76">
+        <v>2</v>
+      </c>
       <c r="H10" s="73"/>
       <c r="I10" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K10" s="41"/>
-      <c r="L10" s="112"/>
+      <c r="L10" s="112">
+        <v>1</v>
+      </c>
       <c r="M10" s="112"/>
-      <c r="N10" s="112"/>
+      <c r="N10" s="112">
+        <v>1</v>
+      </c>
       <c r="O10" s="112"/>
       <c r="P10" s="112"/>
       <c r="Q10" s="120"/>
       <c r="R10" s="99">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" s="126">
         <f t="shared" si="1"/>
@@ -23586,15 +23606,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="107">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V10" s="134">
         <f>U10/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2112</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -23629,30 +23649,38 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>41</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
-      <c r="G11" s="76"/>
+      <c r="G11" s="76">
+        <v>3</v>
+      </c>
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11" s="41"/>
-      <c r="L11" s="112"/>
+      <c r="L11" s="112">
+        <v>2</v>
+      </c>
       <c r="M11" s="112"/>
-      <c r="N11" s="112"/>
+      <c r="N11" s="112">
+        <v>1</v>
+      </c>
       <c r="O11" s="112"/>
       <c r="P11" s="112"/>
       <c r="Q11" s="120"/>
       <c r="R11" s="86">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" s="124">
         <f t="shared" si="1"/>
@@ -23661,15 +23689,15 @@
       <c r="T11" s="41"/>
       <c r="U11" s="107">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V11" s="130">
         <f>U11/24</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>912</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -23704,19 +23732,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>9</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -23744,7 +23776,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -23779,47 +23811,65 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3288</v>
+      </c>
+      <c r="D13" s="114">
+        <v>26</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>43</v>
+      </c>
+      <c r="H13" s="79">
+        <v>23</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3245</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
+      <c r="L13" s="121">
+        <v>14</v>
+      </c>
+      <c r="M13" s="121">
+        <v>5</v>
+      </c>
+      <c r="N13" s="121">
+        <v>17</v>
+      </c>
+      <c r="O13" s="121">
+        <v>18</v>
+      </c>
+      <c r="P13" s="121">
+        <v>12</v>
+      </c>
       <c r="Q13" s="122"/>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>77883</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -23861,19 +23911,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" ref="J14:J59" si="7">D14-H14</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -23901,7 +23955,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -23936,7 +23990,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>2</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -23944,7 +24000,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="7"/>
@@ -23976,7 +24032,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -24161,7 +24217,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -24169,7 +24227,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="7"/>
@@ -24201,7 +24259,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -24311,19 +24369,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -24351,7 +24413,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -24386,7 +24448,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -24394,7 +24458,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="7"/>
@@ -24426,7 +24490,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -24461,7 +24525,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -24469,7 +24535,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="7"/>
@@ -24501,7 +24567,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -24536,19 +24602,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -24576,7 +24646,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -24618,19 +24688,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -24658,7 +24732,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -24700,7 +24774,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>5</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -24708,7 +24784,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="7"/>
@@ -24740,7 +24816,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -24775,30 +24851,38 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>44</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
-      <c r="G26" s="76"/>
+      <c r="G26" s="76">
+        <v>1</v>
+      </c>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
       <c r="M26" s="112"/>
-      <c r="N26" s="112"/>
+      <c r="N26" s="112">
+        <v>1</v>
+      </c>
       <c r="O26" s="112"/>
       <c r="P26" s="112"/>
       <c r="Q26" s="120"/>
       <c r="R26" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" s="124">
         <f t="shared" si="8"/>
@@ -24807,15 +24891,15 @@
       <c r="T26" s="41"/>
       <c r="U26" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V26" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -24831,22 +24915,28 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="110"/>
+      <c r="C27" s="110">
+        <v>2</v>
+      </c>
       <c r="D27" s="111"/>
       <c r="E27" s="112"/>
       <c r="F27" s="112"/>
-      <c r="G27" s="76"/>
+      <c r="G27" s="76">
+        <v>1</v>
+      </c>
       <c r="H27" s="73"/>
       <c r="I27" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="77">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K27" s="42"/>
-      <c r="L27" s="112"/>
+      <c r="L27" s="112">
+        <v>1</v>
+      </c>
       <c r="M27" s="112"/>
       <c r="N27" s="112"/>
       <c r="O27" s="112"/>
@@ -24854,7 +24944,7 @@
       <c r="Q27" s="120"/>
       <c r="R27" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" s="124">
         <f t="shared" si="8"/>
@@ -24863,15 +24953,15 @@
       <c r="T27" s="42"/>
       <c r="U27" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V27" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X27" s="27"/>
       <c r="Y27" s="2"/>
@@ -24890,7 +24980,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>3</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -24898,7 +24990,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="7"/>
@@ -24930,7 +25022,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -25008,30 +25100,38 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>24</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
-      <c r="G30" s="76"/>
+      <c r="G30" s="76">
+        <v>1</v>
+      </c>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
       <c r="M30" s="112"/>
-      <c r="N30" s="112"/>
+      <c r="N30" s="112">
+        <v>1</v>
+      </c>
       <c r="O30" s="112"/>
       <c r="P30" s="112"/>
       <c r="Q30" s="120"/>
       <c r="R30" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" s="124">
         <f t="shared" si="8"/>
@@ -25040,15 +25140,15 @@
       <c r="T30" s="41"/>
       <c r="U30" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V30" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>557</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -25060,7 +25160,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>11</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
@@ -25068,7 +25170,7 @@
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="7"/>
@@ -25100,7 +25202,7 @@
       </c>
       <c r="W31" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -25216,22 +25318,28 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>2</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
-      <c r="G34" s="76"/>
+      <c r="G34" s="76">
+        <v>1</v>
+      </c>
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="77">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K34" s="41"/>
-      <c r="L34" s="112"/>
+      <c r="L34" s="112">
+        <v>1</v>
+      </c>
       <c r="M34" s="112"/>
       <c r="N34" s="112"/>
       <c r="O34" s="112"/>
@@ -25239,7 +25347,7 @@
       <c r="Q34" s="120"/>
       <c r="R34" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" s="124">
         <f t="shared" si="8"/>
@@ -25248,15 +25356,15 @@
       <c r="T34" s="41"/>
       <c r="U34" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V34" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -25268,30 +25376,42 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>189</v>
+      </c>
+      <c r="D35" s="111">
+        <v>2</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
-      <c r="G35" s="76"/>
+      <c r="G35" s="76">
+        <v>7</v>
+      </c>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" s="41"/>
-      <c r="L35" s="112"/>
+      <c r="L35" s="112">
+        <v>5</v>
+      </c>
       <c r="M35" s="112"/>
-      <c r="N35" s="112"/>
+      <c r="N35" s="112">
+        <v>1</v>
+      </c>
       <c r="O35" s="112"/>
-      <c r="P35" s="112"/>
+      <c r="P35" s="112">
+        <v>1</v>
+      </c>
       <c r="Q35" s="120"/>
       <c r="R35" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S35" s="124">
         <f t="shared" si="8"/>
@@ -25300,15 +25420,15 @@
       <c r="T35" s="41"/>
       <c r="U35" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V35" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W35" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>4370</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -25424,30 +25544,42 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>3097</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>253</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2844</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
+      <c r="L38" s="121">
+        <v>96</v>
+      </c>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>24</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>133</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="8"/>
@@ -25456,15 +25588,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>1518</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>17065</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -25476,11 +25608,15 @@
       <c r="B39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="110"/>
+      <c r="C39" s="110">
+        <v>1</v>
+      </c>
       <c r="D39" s="111"/>
       <c r="E39" s="112"/>
       <c r="F39" s="112"/>
-      <c r="G39" s="76"/>
+      <c r="G39" s="76">
+        <v>1</v>
+      </c>
       <c r="H39" s="73"/>
       <c r="I39" s="93">
         <f t="shared" si="4"/>
@@ -25491,7 +25627,9 @@
         <v>0</v>
       </c>
       <c r="K39" s="41"/>
-      <c r="L39" s="112"/>
+      <c r="L39" s="112">
+        <v>1</v>
+      </c>
       <c r="M39" s="112"/>
       <c r="N39" s="112"/>
       <c r="O39" s="112"/>
@@ -25499,7 +25637,7 @@
       <c r="Q39" s="120"/>
       <c r="R39" s="96">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" s="126">
         <f t="shared" si="8"/>
@@ -25508,11 +25646,11 @@
       <c r="T39" s="41"/>
       <c r="U39" s="107">
         <f t="shared" ref="U39:U41" si="10">L39*24+N39*24+P39*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V39" s="109">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W39" s="129">
         <f t="shared" ref="W39:W41" si="11">I39*24+J39</f>
@@ -25580,22 +25718,30 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>312</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
-      <c r="G41" s="149"/>
+      <c r="G41" s="149">
+        <v>5</v>
+      </c>
       <c r="H41" s="150"/>
       <c r="I41" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="153"/>
-      <c r="L41" s="154"/>
+      <c r="L41" s="154">
+        <v>5</v>
+      </c>
       <c r="M41" s="154"/>
       <c r="N41" s="154"/>
       <c r="O41" s="154"/>
@@ -25603,7 +25749,7 @@
       <c r="Q41" s="155"/>
       <c r="R41" s="156">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S41" s="157">
         <f t="shared" si="8"/>
@@ -25612,15 +25758,15 @@
       <c r="T41" s="153"/>
       <c r="U41" s="158">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V41" s="159">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W41" s="159">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>7388</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -25632,30 +25778,40 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>463</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>17</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="181">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>446</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K42" s="169"/>
-      <c r="L42" s="165"/>
+      <c r="L42" s="165">
+        <v>3</v>
+      </c>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>2</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>12</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="8"/>
@@ -25664,15 +25820,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>5352</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -25727,30 +25883,42 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>39092</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>1430</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="182">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37662</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>409</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>501</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>520</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1430</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="8"/>
@@ -25759,15 +25927,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>8580</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>1430</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>225975</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -25823,11 +25991,15 @@
       <c r="B46" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="110"/>
+      <c r="C46" s="110">
+        <v>1</v>
+      </c>
       <c r="D46" s="111"/>
       <c r="E46" s="112"/>
       <c r="F46" s="112"/>
-      <c r="G46" s="76"/>
+      <c r="G46" s="76">
+        <v>1</v>
+      </c>
       <c r="H46" s="73"/>
       <c r="I46" s="93">
         <f t="shared" si="4"/>
@@ -25838,7 +26010,9 @@
         <v>0</v>
       </c>
       <c r="K46" s="41"/>
-      <c r="L46" s="112"/>
+      <c r="L46" s="112">
+        <v>1</v>
+      </c>
       <c r="M46" s="112"/>
       <c r="N46" s="112"/>
       <c r="O46" s="112"/>
@@ -25846,7 +26020,7 @@
       <c r="Q46" s="120"/>
       <c r="R46" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" s="128">
         <f t="shared" si="8"/>
@@ -25855,11 +26029,11 @@
       <c r="T46" s="41"/>
       <c r="U46" s="107">
         <f t="shared" ref="U46:U47" si="12">L46*24+N46*24+P46*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V46" s="134">
         <f t="shared" ref="V46:V47" si="13">U46/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" s="129">
         <f t="shared" ref="W46:W47" si="14">I46*24+J46</f>
@@ -25927,19 +26101,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2686</v>
+      </c>
+      <c r="D48" s="142">
+        <v>3</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
       <c r="G48" s="143"/>
       <c r="H48" s="139"/>
       <c r="I48" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2686</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
@@ -25967,7 +26145,7 @@
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16119</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -25979,7 +26157,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -25987,7 +26167,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="7"/>
@@ -26019,7 +26199,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -26135,7 +26315,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -26143,7 +26325,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="78">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="7"/>
@@ -26175,7 +26357,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -26240,7 +26422,7 @@
         <v>78</v>
       </c>
       <c r="C54" s="110">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
@@ -26249,7 +26431,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="7"/>
@@ -26281,7 +26463,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="20"/>
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -26496,11 +26678,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>9</v>
+        <v>49576</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -26509,40 +26691,40 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1771</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>9</v>
+        <v>47805</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>544</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>549</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="21"/>
@@ -26550,24 +26732,24 @@
       </c>
       <c r="R60" s="85">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1771</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>12006</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
+        <v>1771</v>
       </c>
       <c r="W60" s="180">
         <f>SUM(W8:W59)</f>
-        <v>216</v>
+        <v>364036</v>
       </c>
       <c r="X60" s="45"/>
     </row>

--- a/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61981DC6-CC54-4792-A4F3-FB97B75D9D3C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8BF57C-0AF3-4398-B4A1-29CAB3E1D596}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="08,14" sheetId="142" r:id="rId12"/>
     <sheet name="08,15" sheetId="144" r:id="rId13"/>
     <sheet name="08,17" sheetId="145" r:id="rId14"/>
-    <sheet name="08,15 (4)" sheetId="146" r:id="rId15"/>
+    <sheet name="08,18" sheetId="146" r:id="rId15"/>
     <sheet name="08,15 (5)" sheetId="147" r:id="rId16"/>
   </sheets>
   <definedNames>
@@ -43,9 +43,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="10">'08,13'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'08,14'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'08,15'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="14">'08,15 (4)'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'08,15 (5)'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'08,17'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'08,18'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -27237,7 +27237,7 @@
         <v>1</v>
       </c>
       <c r="P1" s="200">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="Q1" s="201"/>
       <c r="R1" s="201"/>
@@ -27491,30 +27491,38 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>33</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
-      <c r="G8" s="76"/>
+      <c r="G8" s="76">
+        <v>1</v>
+      </c>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8+E8-G8</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
       <c r="M8" s="112"/>
-      <c r="N8" s="112"/>
+      <c r="N8" s="112">
+        <v>1</v>
+      </c>
       <c r="O8" s="112"/>
       <c r="P8" s="112"/>
       <c r="Q8" s="120"/>
       <c r="R8" s="86">
         <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="124">
         <f t="shared" si="1"/>
@@ -27523,15 +27531,15 @@
       <c r="T8" s="41"/>
       <c r="U8" s="107">
         <f>L8*24+N8*24+P8*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V8" s="130">
         <f>U8/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>777</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -27566,19 +27574,23 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
-      <c r="D9" s="114"/>
+      <c r="C9" s="113">
+        <v>80</v>
+      </c>
+      <c r="D9" s="114">
+        <v>12</v>
+      </c>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
       <c r="G9" s="78"/>
       <c r="H9" s="79"/>
       <c r="I9" s="80">
         <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K9" s="51"/>
       <c r="L9" s="121"/>
@@ -27606,7 +27618,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1932</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -27641,15 +27653,19 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>88</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
-      <c r="G10" s="76"/>
+      <c r="G10" s="76">
+        <v>1</v>
+      </c>
       <c r="H10" s="73"/>
       <c r="I10" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -27658,13 +27674,15 @@
       <c r="K10" s="41"/>
       <c r="L10" s="112"/>
       <c r="M10" s="112"/>
-      <c r="N10" s="112"/>
+      <c r="N10" s="112">
+        <v>1</v>
+      </c>
       <c r="O10" s="112"/>
       <c r="P10" s="112"/>
       <c r="Q10" s="120"/>
       <c r="R10" s="99">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="126">
         <f t="shared" si="1"/>
@@ -27673,15 +27691,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="107">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V10" s="134">
         <f>U10/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2088</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -27716,15 +27734,19 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>38</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
-      <c r="G11" s="76"/>
+      <c r="G11" s="76">
+        <v>2</v>
+      </c>
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
@@ -27733,13 +27755,17 @@
       <c r="K11" s="41"/>
       <c r="L11" s="112"/>
       <c r="M11" s="112"/>
-      <c r="N11" s="112"/>
+      <c r="N11" s="112">
+        <v>1</v>
+      </c>
       <c r="O11" s="112"/>
-      <c r="P11" s="112"/>
+      <c r="P11" s="112">
+        <v>1</v>
+      </c>
       <c r="Q11" s="120"/>
       <c r="R11" s="86">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" s="124">
         <f t="shared" si="1"/>
@@ -27748,15 +27774,15 @@
       <c r="T11" s="41"/>
       <c r="U11" s="107">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V11" s="130">
         <f>U11/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>864</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -27791,19 +27817,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>9</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -27831,7 +27861,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -27866,47 +27896,65 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3245</v>
+      </c>
+      <c r="D13" s="114">
+        <v>3</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>26</v>
+      </c>
+      <c r="H13" s="79">
+        <v>25</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3219</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
+      <c r="L13" s="121">
+        <v>10</v>
+      </c>
+      <c r="M13" s="121">
+        <v>4</v>
+      </c>
+      <c r="N13" s="121">
+        <v>7</v>
+      </c>
+      <c r="O13" s="121">
+        <v>21</v>
+      </c>
+      <c r="P13" s="121">
+        <v>9</v>
+      </c>
       <c r="Q13" s="122"/>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>624</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>77234</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -27948,19 +27996,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" ref="J14:J59" si="7">D14-H14</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -27988,7 +28040,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -28023,7 +28075,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>2</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -28031,7 +28085,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="7"/>
@@ -28063,7 +28117,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -28248,7 +28302,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -28256,7 +28312,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="7"/>
@@ -28288,7 +28344,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -28398,19 +28454,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -28438,7 +28498,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -28473,7 +28533,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -28481,7 +28543,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="7"/>
@@ -28513,7 +28575,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -28548,7 +28610,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -28556,7 +28620,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="7"/>
@@ -28588,7 +28652,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -28623,19 +28687,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -28663,7 +28731,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -28705,19 +28773,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -28745,7 +28817,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -28787,7 +28859,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>5</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -28795,7 +28869,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="7"/>
@@ -28827,7 +28901,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -28862,19 +28936,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>43</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
       <c r="G26" s="76"/>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
@@ -28902,7 +28980,7 @@
       </c>
       <c r="W26" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -28918,11 +28996,15 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="110"/>
+      <c r="C27" s="110">
+        <v>1</v>
+      </c>
       <c r="D27" s="111"/>
       <c r="E27" s="112"/>
       <c r="F27" s="112"/>
-      <c r="G27" s="76"/>
+      <c r="G27" s="76">
+        <v>1</v>
+      </c>
       <c r="H27" s="73"/>
       <c r="I27" s="73">
         <f t="shared" si="4"/>
@@ -28937,11 +29019,13 @@
       <c r="M27" s="112"/>
       <c r="N27" s="112"/>
       <c r="O27" s="112"/>
-      <c r="P27" s="112"/>
+      <c r="P27" s="112">
+        <v>1</v>
+      </c>
       <c r="Q27" s="120"/>
       <c r="R27" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" s="124">
         <f t="shared" si="8"/>
@@ -28950,11 +29034,11 @@
       <c r="T27" s="42"/>
       <c r="U27" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V27" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="129">
         <f t="shared" si="9"/>
@@ -28977,7 +29061,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>3</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -28985,7 +29071,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="7"/>
@@ -29017,7 +29103,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -29095,19 +29181,23 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>23</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
       <c r="G30" s="76"/>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
@@ -29135,7 +29225,7 @@
       </c>
       <c r="W30" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>557</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -29147,15 +29237,19 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>11</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
-      <c r="G31" s="76"/>
+      <c r="G31" s="76">
+        <v>1</v>
+      </c>
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="7"/>
@@ -29164,13 +29258,15 @@
       <c r="K31" s="41"/>
       <c r="L31" s="112"/>
       <c r="M31" s="112"/>
-      <c r="N31" s="112"/>
+      <c r="N31" s="112">
+        <v>1</v>
+      </c>
       <c r="O31" s="112"/>
       <c r="P31" s="112"/>
       <c r="Q31" s="120"/>
       <c r="R31" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="124">
         <f t="shared" si="8"/>
@@ -29179,15 +29275,15 @@
       <c r="T31" s="41"/>
       <c r="U31" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V31" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -29303,7 +29399,9 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>1</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
@@ -29311,7 +29409,7 @@
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="77">
         <f t="shared" si="7"/>
@@ -29343,7 +29441,7 @@
       </c>
       <c r="W34" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -29355,19 +29453,23 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>182</v>
+      </c>
+      <c r="D35" s="111">
+        <v>2</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
       <c r="G35" s="76"/>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="112"/>
@@ -29395,7 +29497,7 @@
       </c>
       <c r="W35" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>4370</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -29511,30 +29613,40 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>2844</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>58</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2786</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
       <c r="L38" s="121"/>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>23</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>35</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="8"/>
@@ -29543,15 +29655,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>16717</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -29667,19 +29779,23 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>307</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
       <c r="G41" s="149"/>
       <c r="H41" s="150"/>
       <c r="I41" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="153"/>
       <c r="L41" s="154"/>
@@ -29707,7 +29823,7 @@
       </c>
       <c r="W41" s="159">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>7388</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -29719,30 +29835,40 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>446</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>16</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="181">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K42" s="169"/>
-      <c r="L42" s="165"/>
+      <c r="L42" s="165">
+        <v>7</v>
+      </c>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>8</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>1</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="8"/>
@@ -29751,15 +29877,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>5160</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -29814,30 +29940,44 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
-      <c r="E44" s="115"/>
+      <c r="C44" s="113">
+        <v>37662</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
+      <c r="E44" s="115">
+        <v>1836</v>
+      </c>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>1206</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="182">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>38292</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>673</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>259</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>274</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1206</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="8"/>
@@ -29846,15 +29986,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>7236</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>1206</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>229755</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -30014,30 +30154,40 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2686</v>
+      </c>
+      <c r="D48" s="142">
+        <v>3</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
-      <c r="G48" s="143"/>
+      <c r="G48" s="143">
+        <v>6</v>
+      </c>
       <c r="H48" s="139"/>
       <c r="I48" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2680</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48" s="51"/>
-      <c r="L48" s="121"/>
+      <c r="L48" s="121">
+        <v>5</v>
+      </c>
       <c r="M48" s="121"/>
-      <c r="N48" s="121"/>
+      <c r="N48" s="121">
+        <v>1</v>
+      </c>
       <c r="O48" s="121"/>
       <c r="P48" s="121"/>
       <c r="Q48" s="122"/>
       <c r="R48" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S48" s="144">
         <f t="shared" si="8"/>
@@ -30046,15 +30196,15 @@
       <c r="T48" s="51"/>
       <c r="U48" s="131">
         <f>L48*6+N48*6+P48*6</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="V48" s="135">
         <f>U48/6</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16083</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -30066,7 +30216,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -30074,7 +30226,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="7"/>
@@ -30106,7 +30258,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -30222,7 +30374,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -30230,7 +30384,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="78">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="7"/>
@@ -30262,7 +30416,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -30327,7 +30481,7 @@
         <v>78</v>
       </c>
       <c r="C54" s="110">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
@@ -30336,7 +30490,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="7"/>
@@ -30368,7 +30522,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="20"/>
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -30583,53 +30737,53 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>9</v>
+        <v>47805</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
-        <v>0</v>
+        <v>1836</v>
       </c>
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1318</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>9</v>
+        <v>48323</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="21"/>
@@ -30637,24 +30791,24 @@
       </c>
       <c r="R60" s="85">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1318</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>8580</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
+        <v>1318</v>
       </c>
       <c r="W60" s="180">
         <f>SUM(W8:W59)</f>
-        <v>216</v>
+        <v>366447</v>
       </c>
       <c r="X60" s="45"/>
     </row>

--- a/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8BF57C-0AF3-4398-B4A1-29CAB3E1D596}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619B3A72-1524-4535-886B-01EC2C8CDDD6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <sheet name="08,15" sheetId="144" r:id="rId13"/>
     <sheet name="08,17" sheetId="145" r:id="rId14"/>
     <sheet name="08,18" sheetId="146" r:id="rId15"/>
-    <sheet name="08,15 (5)" sheetId="147" r:id="rId16"/>
+    <sheet name="08,19" sheetId="147" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'08,03'!$A$1:$Y$61</definedName>
@@ -43,9 +43,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="10">'08,13'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'08,14'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'08,15'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'08,15 (5)'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'08,17'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'08,18'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'08,19'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -31296,7 +31296,7 @@
         <v>1</v>
       </c>
       <c r="P1" s="200">
-        <v>46249</v>
+        <v>46253</v>
       </c>
       <c r="Q1" s="201"/>
       <c r="R1" s="201"/>
@@ -31550,19 +31550,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>32</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8+E8-G8</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -31590,7 +31594,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>777</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -31625,30 +31629,38 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
-      <c r="D9" s="114"/>
+      <c r="C9" s="113">
+        <v>80</v>
+      </c>
+      <c r="D9" s="114">
+        <v>12</v>
+      </c>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
-      <c r="G9" s="78"/>
+      <c r="G9" s="78">
+        <v>1</v>
+      </c>
       <c r="H9" s="79"/>
       <c r="I9" s="80">
         <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K9" s="51"/>
       <c r="L9" s="121"/>
       <c r="M9" s="121"/>
       <c r="N9" s="121"/>
       <c r="O9" s="121"/>
-      <c r="P9" s="121"/>
+      <c r="P9" s="121">
+        <v>1</v>
+      </c>
       <c r="Q9" s="122"/>
       <c r="R9" s="98">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="125">
         <f t="shared" si="1"/>
@@ -31657,15 +31669,15 @@
       <c r="T9" s="51"/>
       <c r="U9" s="131">
         <f>L9*24+N9*24+P9*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V9" s="132">
         <f>U9/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1908</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -31700,22 +31712,28 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>87</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
-      <c r="G10" s="76"/>
+      <c r="G10" s="76">
+        <v>6</v>
+      </c>
       <c r="H10" s="73"/>
       <c r="I10" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K10" s="41"/>
-      <c r="L10" s="112"/>
+      <c r="L10" s="112">
+        <v>6</v>
+      </c>
       <c r="M10" s="112"/>
       <c r="N10" s="112"/>
       <c r="O10" s="112"/>
@@ -31723,7 +31741,7 @@
       <c r="Q10" s="120"/>
       <c r="R10" s="99">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S10" s="126">
         <f t="shared" si="1"/>
@@ -31732,15 +31750,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="107">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V10" s="134">
         <f>U10/24</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1944</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -31775,22 +31793,28 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>36</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
-      <c r="G11" s="76"/>
+      <c r="G11" s="76">
+        <v>6</v>
+      </c>
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11" s="41"/>
-      <c r="L11" s="112"/>
+      <c r="L11" s="112">
+        <v>6</v>
+      </c>
       <c r="M11" s="112"/>
       <c r="N11" s="112"/>
       <c r="O11" s="112"/>
@@ -31798,7 +31822,7 @@
       <c r="Q11" s="120"/>
       <c r="R11" s="86">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S11" s="124">
         <f t="shared" si="1"/>
@@ -31807,15 +31831,15 @@
       <c r="T11" s="41"/>
       <c r="U11" s="107">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V11" s="130">
         <f>U11/24</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -31850,19 +31874,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>9</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -31890,7 +31918,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -31925,47 +31953,67 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3218</v>
+      </c>
+      <c r="D13" s="114">
+        <v>2</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>23</v>
+      </c>
+      <c r="H13" s="79">
+        <v>12</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3195</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
+      <c r="L13" s="121">
+        <v>2</v>
+      </c>
+      <c r="M13" s="121">
+        <v>4</v>
+      </c>
+      <c r="N13" s="121">
+        <v>12</v>
+      </c>
+      <c r="O13" s="121">
+        <v>3</v>
+      </c>
+      <c r="P13" s="121">
+        <v>9</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>5</v>
+      </c>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>76670</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -32007,19 +32055,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" ref="J14:J59" si="7">D14-H14</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -32047,7 +32099,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -32082,7 +32134,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>2</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -32090,7 +32144,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="7"/>
@@ -32122,7 +32176,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -32307,7 +32361,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -32315,7 +32371,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="7"/>
@@ -32347,7 +32403,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -32457,19 +32513,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -32497,7 +32557,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -32532,7 +32592,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -32540,7 +32602,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="7"/>
@@ -32572,7 +32634,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -32607,7 +32669,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -32615,7 +32679,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="7"/>
@@ -32647,7 +32711,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -32682,19 +32746,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -32722,7 +32790,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -32764,19 +32832,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -32804,7 +32876,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -32846,7 +32918,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>5</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -32854,7 +32928,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="7"/>
@@ -32886,7 +32960,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -32921,22 +32995,32 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="112"/>
+      <c r="C26" s="110">
+        <v>43</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
+      <c r="E26" s="112">
+        <v>126</v>
+      </c>
       <c r="F26" s="112"/>
-      <c r="G26" s="76"/>
+      <c r="G26" s="76">
+        <v>3</v>
+      </c>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
-      <c r="L26" s="112"/>
+      <c r="L26" s="112">
+        <v>3</v>
+      </c>
       <c r="M26" s="112"/>
       <c r="N26" s="112"/>
       <c r="O26" s="112"/>
@@ -32944,7 +33028,7 @@
       <c r="Q26" s="120"/>
       <c r="R26" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S26" s="124">
         <f t="shared" si="8"/>
@@ -32953,15 +33037,15 @@
       <c r="T26" s="41"/>
       <c r="U26" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V26" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W26" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3985</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -33036,7 +33120,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>3</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -33044,7 +33130,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="7"/>
@@ -33076,7 +33162,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -33154,22 +33240,30 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>23</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
-      <c r="G30" s="76"/>
+      <c r="G30" s="76">
+        <v>1</v>
+      </c>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
-      <c r="L30" s="112"/>
+      <c r="L30" s="112">
+        <v>1</v>
+      </c>
       <c r="M30" s="112"/>
       <c r="N30" s="112"/>
       <c r="O30" s="112"/>
@@ -33177,7 +33271,7 @@
       <c r="Q30" s="120"/>
       <c r="R30" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" s="124">
         <f t="shared" si="8"/>
@@ -33186,15 +33280,15 @@
       <c r="T30" s="41"/>
       <c r="U30" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V30" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>533</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -33206,22 +33300,28 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>10</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
-      <c r="G31" s="76"/>
+      <c r="G31" s="76">
+        <v>2</v>
+      </c>
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K31" s="41"/>
-      <c r="L31" s="112"/>
+      <c r="L31" s="112">
+        <v>2</v>
+      </c>
       <c r="M31" s="112"/>
       <c r="N31" s="112"/>
       <c r="O31" s="112"/>
@@ -33229,7 +33329,7 @@
       <c r="Q31" s="120"/>
       <c r="R31" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S31" s="124">
         <f t="shared" si="8"/>
@@ -33238,15 +33338,15 @@
       <c r="T31" s="41"/>
       <c r="U31" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V31" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W31" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -33362,11 +33462,15 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>1</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
-      <c r="G34" s="76"/>
+      <c r="G34" s="76">
+        <v>1</v>
+      </c>
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
@@ -33377,7 +33481,9 @@
         <v>0</v>
       </c>
       <c r="K34" s="41"/>
-      <c r="L34" s="112"/>
+      <c r="L34" s="112">
+        <v>1</v>
+      </c>
       <c r="M34" s="112"/>
       <c r="N34" s="112"/>
       <c r="O34" s="112"/>
@@ -33385,7 +33491,7 @@
       <c r="Q34" s="120"/>
       <c r="R34" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" s="124">
         <f t="shared" si="8"/>
@@ -33394,11 +33500,11 @@
       <c r="T34" s="41"/>
       <c r="U34" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V34" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" s="129">
         <f t="shared" si="9"/>
@@ -33414,30 +33520,38 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>182</v>
+      </c>
+      <c r="D35" s="111">
+        <v>2</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
-      <c r="G35" s="76"/>
+      <c r="G35" s="76">
+        <v>1</v>
+      </c>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="112"/>
       <c r="M35" s="112"/>
       <c r="N35" s="112"/>
       <c r="O35" s="112"/>
-      <c r="P35" s="112"/>
+      <c r="P35" s="112">
+        <v>1</v>
+      </c>
       <c r="Q35" s="120"/>
       <c r="R35" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" s="124">
         <f t="shared" si="8"/>
@@ -33446,15 +33560,15 @@
       <c r="T35" s="41"/>
       <c r="U35" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V35" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>4346</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -33570,30 +33684,42 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
-      <c r="E38" s="115"/>
+      <c r="C38" s="113">
+        <v>2786</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
+      <c r="E38" s="115">
+        <v>864</v>
+      </c>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>126</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3524</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
+      <c r="L38" s="121">
+        <v>62</v>
+      </c>
       <c r="M38" s="121"/>
       <c r="N38" s="121"/>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>64</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="8"/>
@@ -33602,15 +33728,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>756</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>21145</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -33726,22 +33852,30 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>307</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
-      <c r="G41" s="149"/>
+      <c r="G41" s="149">
+        <v>47</v>
+      </c>
       <c r="H41" s="150"/>
       <c r="I41" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="153"/>
-      <c r="L41" s="154"/>
+      <c r="L41" s="154">
+        <v>47</v>
+      </c>
       <c r="M41" s="154"/>
       <c r="N41" s="154"/>
       <c r="O41" s="154"/>
@@ -33749,7 +33883,7 @@
       <c r="Q41" s="155"/>
       <c r="R41" s="156">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="S41" s="157">
         <f t="shared" si="8"/>
@@ -33758,15 +33892,15 @@
       <c r="T41" s="153"/>
       <c r="U41" s="158">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="V41" s="159">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="W41" s="159">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>6260</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -33778,30 +33912,38 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>430</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>25</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="181">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K42" s="169"/>
-      <c r="L42" s="165"/>
+      <c r="L42" s="165">
+        <v>10</v>
+      </c>
       <c r="M42" s="165"/>
       <c r="N42" s="165"/>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>15</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="8"/>
@@ -33810,15 +33952,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>4860</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -33873,30 +34015,44 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
-      <c r="E44" s="115"/>
+      <c r="C44" s="113">
+        <v>38290</v>
+      </c>
+      <c r="D44" s="114">
+        <v>2</v>
+      </c>
+      <c r="E44" s="115">
+        <v>2592</v>
+      </c>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>1015</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="182">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>39867</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>368</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>330</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>317</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="8"/>
@@ -33905,15 +34061,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>6090</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>239204</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -34073,19 +34229,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2680</v>
+      </c>
+      <c r="D48" s="142">
+        <v>3</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
       <c r="G48" s="143"/>
       <c r="H48" s="139"/>
       <c r="I48" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2680</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
@@ -34113,7 +34273,7 @@
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16083</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -34125,7 +34285,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -34133,7 +34295,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="7"/>
@@ -34165,7 +34327,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -34281,7 +34443,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -34289,7 +34453,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="78">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="7"/>
@@ -34321,7 +34485,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -34386,7 +34550,7 @@
         <v>78</v>
       </c>
       <c r="C54" s="110">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
@@ -34395,7 +34559,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="7"/>
@@ -34427,7 +34591,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="20"/>
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -34642,78 +34806,78 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>9</v>
+        <v>48320</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
-        <v>0</v>
+        <v>3582</v>
       </c>
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1257</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>9</v>
+        <v>50645</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R60" s="85">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1257</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>9330</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
+        <v>1257</v>
       </c>
       <c r="W60" s="180">
         <f>SUM(W8:W59)</f>
-        <v>216</v>
+        <v>380852</v>
       </c>
       <c r="X60" s="45"/>
     </row>

--- a/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619B3A72-1524-4535-886B-01EC2C8CDDD6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789FE225-EEFA-493D-BFDD-7CA5E5F1065E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="08,17" sheetId="145" r:id="rId14"/>
     <sheet name="08,18" sheetId="146" r:id="rId15"/>
     <sheet name="08,19" sheetId="147" r:id="rId16"/>
+    <sheet name="08,20" sheetId="148" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'08,03'!$A$1:$Y$61</definedName>
@@ -46,6 +47,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="13">'08,17'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'08,18'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'08,19'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'08,20'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -723,6 +725,92 @@
       </text>
     </comment>
     <comment ref="W5" authorId="0" shapeId="0" xr:uid="{F6A181B7-C36B-46D4-85BF-B8F937EFEDD9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments17.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{B4286E9F-5447-4EA2-B970-5CC3F3D153C0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{1A70275C-001F-4068-9EF3-D801EDAA33C0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{990CC5E2-31DD-459B-93B7-8EE538955344}">
       <text>
         <r>
           <rPr>
@@ -1440,7 +1528,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -3048,7 +3136,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="218">
+  <cellXfs count="221">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3632,6 +3720,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4071,15 +4168,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200"/>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="P1" s="203"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -4104,62 +4201,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -6410,7 +6507,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -6428,7 +6525,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -6444,7 +6541,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -6460,7 +6557,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -6478,7 +6575,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -6494,7 +6591,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -6889,17 +6986,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46246</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -6924,62 +7021,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -10475,7 +10572,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -10493,7 +10590,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -10509,7 +10606,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -10525,7 +10622,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -10543,7 +10640,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -10559,7 +10656,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -10954,17 +11051,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46247</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -10989,62 +11086,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -14554,7 +14651,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -14572,7 +14669,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -14588,7 +14685,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -14604,7 +14701,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -14622,7 +14719,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -14638,7 +14735,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -15033,17 +15130,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46248</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -15068,62 +15165,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -18633,7 +18730,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -18651,7 +18748,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -18667,7 +18764,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -18683,7 +18780,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -18701,7 +18798,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -18717,7 +18814,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -19112,17 +19209,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46249</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -19147,62 +19244,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="194" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -22670,7 +22767,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -22688,7 +22785,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -22704,7 +22801,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -22720,7 +22817,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -22738,7 +22835,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -22754,7 +22851,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -23149,17 +23246,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46251</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -23184,62 +23281,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="194" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -26757,7 +26854,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -26775,7 +26872,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -26791,7 +26888,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -26807,7 +26904,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -26825,7 +26922,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -26841,7 +26938,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -27236,17 +27333,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46252</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -27271,62 +27368,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="194" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -30816,7 +30913,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -30834,7 +30931,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -30850,7 +30947,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -30866,7 +30963,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -30884,7 +30981,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -30900,7 +30997,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -31295,17 +31392,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46253</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -31330,62 +31427,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="194" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -34885,7 +34982,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -34903,7 +35000,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -34919,7 +35016,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -34935,7 +35032,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -34953,7 +35050,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -34969,7 +35066,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -34993,6 +35090,4097 @@
         <v>3</v>
       </c>
       <c r="D69" s="193"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80482285-96FD-4DCB-9ED2-3AC211F72AC4}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="203">
+        <v>46253</v>
+      </c>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="206" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="207" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="208" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="209" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="213" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="215" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="213" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="217" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="197" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110">
+        <v>32</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8+E8-G8</f>
+        <v>32</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>9</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="129">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>777</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113">
+        <v>79</v>
+      </c>
+      <c r="D9" s="114">
+        <v>12</v>
+      </c>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78">
+        <v>3</v>
+      </c>
+      <c r="H9" s="79"/>
+      <c r="I9" s="80">
+        <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
+        <v>76</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121">
+        <v>3</v>
+      </c>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>72</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>3</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" si="2"/>
+        <v>1836</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110">
+        <v>81</v>
+      </c>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76">
+        <v>10</v>
+      </c>
+      <c r="H10" s="73"/>
+      <c r="I10" s="93">
+        <f t="shared" si="4"/>
+        <v>71</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112">
+        <v>10</v>
+      </c>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>240</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>10</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="2"/>
+        <v>1704</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110">
+        <v>30</v>
+      </c>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76">
+        <v>10</v>
+      </c>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112">
+        <v>10</v>
+      </c>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>240</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>10</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="2"/>
+        <v>480</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110">
+        <v>9</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76">
+        <v>9</v>
+      </c>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112">
+        <v>9</v>
+      </c>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>216</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>9</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113">
+        <v>3194</v>
+      </c>
+      <c r="D13" s="114">
+        <v>14</v>
+      </c>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78">
+        <v>34</v>
+      </c>
+      <c r="H13" s="79">
+        <v>16</v>
+      </c>
+      <c r="I13" s="80">
+        <f t="shared" si="4"/>
+        <v>3160</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>-2</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121">
+        <v>12</v>
+      </c>
+      <c r="M13" s="121">
+        <v>10</v>
+      </c>
+      <c r="N13" s="121">
+        <v>3</v>
+      </c>
+      <c r="O13" s="121">
+        <v>6</v>
+      </c>
+      <c r="P13" s="121">
+        <v>19</v>
+      </c>
+      <c r="Q13" s="122"/>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>34</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>16</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>816</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>34</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>75838</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" ref="J14:J59" si="7">D14-H14</f>
+        <v>16</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="8">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
+        <v>64</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110">
+        <v>2</v>
+      </c>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="9"/>
+        <v>48</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="9"/>
+        <v>72</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76">
+        <v>1</v>
+      </c>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="9"/>
+        <v>68</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="9"/>
+        <v>120</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="9"/>
+        <v>48</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76">
+        <v>1</v>
+      </c>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112">
+        <v>1</v>
+      </c>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="9"/>
+        <v>44</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="9"/>
+        <v>907</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110">
+        <v>5</v>
+      </c>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="9"/>
+        <v>120</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="110">
+        <v>166</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76">
+        <v>4</v>
+      </c>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="4"/>
+        <v>162</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112">
+        <v>2</v>
+      </c>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>96</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="9"/>
+        <v>3889</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110">
+        <v>3</v>
+      </c>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76">
+        <v>1</v>
+      </c>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112">
+        <v>1</v>
+      </c>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="9"/>
+        <v>48</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112"/>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110">
+        <v>22</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76">
+        <v>14</v>
+      </c>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112">
+        <v>11</v>
+      </c>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112">
+        <v>2</v>
+      </c>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="8"/>
+        <v>14</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>336</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>14</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="9"/>
+        <v>197</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110">
+        <v>8</v>
+      </c>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76">
+        <v>4</v>
+      </c>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112">
+        <v>3</v>
+      </c>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>96</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110"/>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110">
+        <v>181</v>
+      </c>
+      <c r="D35" s="111">
+        <v>2</v>
+      </c>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76">
+        <v>13</v>
+      </c>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="4"/>
+        <v>168</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112">
+        <v>11</v>
+      </c>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112">
+        <v>2</v>
+      </c>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112"/>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="8"/>
+        <v>13</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>312</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="9"/>
+        <v>4034</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113">
+        <v>3524</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78">
+        <v>179</v>
+      </c>
+      <c r="H38" s="79"/>
+      <c r="I38" s="80">
+        <f t="shared" si="4"/>
+        <v>3345</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121">
+        <v>48</v>
+      </c>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121">
+        <v>21</v>
+      </c>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121">
+        <v>110</v>
+      </c>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="8"/>
+        <v>179</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>1074</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>179</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>20071</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="10">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="11">I39*24+J39</f>
+        <v>0</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146">
+        <v>260</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149">
+        <v>3</v>
+      </c>
+      <c r="H41" s="150"/>
+      <c r="I41" s="80">
+        <f t="shared" si="4"/>
+        <v>257</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154">
+        <v>1</v>
+      </c>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154"/>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154">
+        <v>2</v>
+      </c>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="10"/>
+        <v>72</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="11"/>
+        <v>6188</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163">
+        <v>405</v>
+      </c>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166">
+        <v>77</v>
+      </c>
+      <c r="H42" s="167"/>
+      <c r="I42" s="181">
+        <f t="shared" si="4"/>
+        <v>328</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165">
+        <v>27</v>
+      </c>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165">
+        <v>6</v>
+      </c>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165">
+        <v>44</v>
+      </c>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="8"/>
+        <v>77</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>924</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>77</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>3936</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113">
+        <v>39867</v>
+      </c>
+      <c r="D44" s="114">
+        <v>2</v>
+      </c>
+      <c r="E44" s="115"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78">
+        <v>1239</v>
+      </c>
+      <c r="H44" s="79"/>
+      <c r="I44" s="182">
+        <f t="shared" si="4"/>
+        <v>38628</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121">
+        <v>703</v>
+      </c>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121">
+        <v>71</v>
+      </c>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121">
+        <v>465</v>
+      </c>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="8"/>
+        <v>1239</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>7434</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>1239</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>231770</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="12">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="13">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="14">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141">
+        <v>2680</v>
+      </c>
+      <c r="D48" s="142">
+        <v>3</v>
+      </c>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143">
+        <v>13</v>
+      </c>
+      <c r="H48" s="139"/>
+      <c r="I48" s="80">
+        <f t="shared" si="4"/>
+        <v>2667</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121">
+        <v>13</v>
+      </c>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="8"/>
+        <v>13</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>78</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>13</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>16005</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="93">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="15">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="16">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="78">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="18">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="19">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="20">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110">
+        <v>7</v>
+      </c>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="20"/>
+        <v>168</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>50644</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>146</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>1615</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>16</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>49029</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>130</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
+        <v>865</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="21"/>
+        <v>10</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="21"/>
+        <v>105</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="21"/>
+        <v>6</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="21"/>
+        <v>645</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="21"/>
+        <v>1615</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="21"/>
+        <v>16</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>12078</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>1615</v>
+      </c>
+      <c r="W60" s="180">
+        <f>SUM(W8:W59)</f>
+        <v>368758</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="198" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="199"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="200"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="201" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="201"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="202"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="195" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="196"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>
@@ -35364,17 +39552,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46237</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -35399,62 +39587,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -38979,7 +43167,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -38997,7 +43185,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -39013,7 +43201,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -39029,7 +43217,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -39047,7 +43235,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -39063,7 +43251,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -39458,17 +43646,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46238</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -39493,62 +43681,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="188" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -43020,7 +47208,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -43038,7 +47226,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -43054,7 +47242,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -43070,7 +47258,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -43088,7 +47276,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -43104,7 +47292,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -43499,17 +47687,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46239</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -43534,62 +47722,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="188" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -47073,7 +51261,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -47091,7 +51279,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -47107,7 +51295,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -47123,7 +51311,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -47141,7 +51329,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -47157,7 +51345,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -47552,17 +51740,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46240</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -47587,62 +51775,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="188" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -51118,7 +55306,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -51136,7 +55324,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -51152,7 +55340,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -51168,7 +55356,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -51186,7 +55374,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -51202,7 +55390,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -51597,17 +55785,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46241</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -51632,62 +55820,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="188" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -55173,7 +59361,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -55191,7 +59379,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -55207,7 +59395,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -55223,7 +59411,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -55241,7 +59429,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -55257,7 +59445,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -55652,17 +59840,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46242</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -55687,62 +59875,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="188" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -59206,7 +63394,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -59224,7 +63412,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -59240,7 +63428,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -59256,7 +63444,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -59274,7 +63462,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -59290,7 +63478,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -59685,17 +63873,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46244</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -59720,62 +63908,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="188" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -63257,7 +67445,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -63275,7 +67463,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -63291,7 +67479,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -63307,7 +67495,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -63325,7 +67513,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -63341,7 +67529,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -63736,17 +67924,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46245</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -63771,62 +67959,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="188" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -67326,7 +71514,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -67344,7 +71532,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -67360,7 +71548,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -67376,7 +71564,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -67394,7 +71582,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -67410,7 +71598,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">

--- a/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/DSSR GBDS MONTH OF AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789FE225-EEFA-493D-BFDD-7CA5E5F1065E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF908AD-7989-4664-B44F-1EC734F7F6CA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
